--- a/branches/migration/2027.0.0-ballot.rc1-template-v0.13.2/all-profiles.xlsx
+++ b/branches/migration/2027.0.0-ballot.rc1-template-v0.13.2/all-profiles.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11373" uniqueCount="1059">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11373" uniqueCount="1061">
   <si>
     <t>Property</t>
   </si>
@@ -1916,6 +1916,13 @@
     <t>resultType</t>
   </si>
   <si>
+    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
+  &lt;coding&gt;
+    &lt;system value="http://fhir.de/ConsentManagement/CodeSystem/ResultType"/&gt;
+  &lt;/coding&gt;
+&lt;/valueCodeableConcept&gt;</t>
+  </si>
+  <si>
     <t>http://fhir.de/ConsentManagement/ValueSet/ResultType</t>
   </si>
   <si>
@@ -1956,6 +1963,13 @@
   </si>
   <si>
     <t>templateType</t>
+  </si>
+  <si>
+    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
+  &lt;coding&gt;
+    &lt;system value="http://fhir.de/ConsentManagement/CodeSystem/TemplateType"/&gt;
+  &lt;/coding&gt;
+&lt;/valueCodeableConcept&gt;</t>
   </si>
   <si>
     <t>http://fhir.de/ConsentManagement/ValueSet/TemplateType</t>
@@ -3756,7 +3770,7 @@
         <v>2</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>888</v>
+        <v>890</v>
       </c>
     </row>
     <row r="45">
@@ -3764,7 +3778,7 @@
         <v>4</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>889</v>
+        <v>891</v>
       </c>
     </row>
     <row r="46">
@@ -3780,7 +3794,7 @@
         <v>8</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>890</v>
+        <v>892</v>
       </c>
     </row>
     <row r="48">
@@ -3788,7 +3802,7 @@
         <v>10</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>891</v>
+        <v>893</v>
       </c>
     </row>
     <row r="49">
@@ -3842,7 +3856,7 @@
         <v>23</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>892</v>
+        <v>894</v>
       </c>
     </row>
     <row r="56">
@@ -3878,7 +3892,7 @@
         <v>31</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>893</v>
+        <v>895</v>
       </c>
     </row>
     <row r="61">
@@ -3886,7 +3900,7 @@
         <v>33</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>894</v>
+        <v>896</v>
       </c>
     </row>
     <row r="62">
@@ -18695,7 +18709,7 @@
         <v>75</v>
       </c>
       <c r="T141" t="s" s="2">
-        <v>75</v>
+        <v>610</v>
       </c>
       <c r="U141" t="s" s="2">
         <v>75</v>
@@ -18714,7 +18728,7 @@
       </c>
       <c r="Z141" s="2"/>
       <c r="AA141" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="AB141" t="s" s="2">
         <v>75</v>
@@ -18752,7 +18766,7 @@
         <v>386</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="C142" t="s" s="2">
         <v>573</v>
@@ -18855,7 +18869,7 @@
         <v>386</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="C143" t="s" s="2">
         <v>575</v>
@@ -18960,7 +18974,7 @@
         <v>386</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="C144" t="s" s="2">
         <v>577</v>
@@ -19067,7 +19081,7 @@
         <v>386</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="C145" t="s" s="2">
         <v>579</v>
@@ -19170,7 +19184,7 @@
         <v>386</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="C146" t="s" s="2">
         <v>581</v>
@@ -19275,7 +19289,7 @@
         <v>386</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="C147" t="s" s="2">
         <v>583</v>
@@ -19382,7 +19396,7 @@
         <v>386</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="C148" t="s" s="2">
         <v>585</v>
@@ -19487,7 +19501,7 @@
         <v>386</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="C149" t="s" s="2">
         <v>587</v>
@@ -19592,7 +19606,7 @@
         <v>386</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="C150" t="s" s="2">
         <v>589</v>
@@ -19697,7 +19711,7 @@
         <v>386</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="C151" t="s" s="2">
         <v>591</v>
@@ -19804,7 +19818,7 @@
         <v>386</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="C152" t="s" s="2">
         <v>593</v>
@@ -19911,13 +19925,13 @@
         <v>386</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="C153" t="s" s="2">
         <v>562</v>
       </c>
       <c r="D153" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="E153" t="s" s="2">
         <v>75</v>
@@ -19957,7 +19971,7 @@
         <v>75</v>
       </c>
       <c r="T153" t="s" s="2">
-        <v>75</v>
+        <v>625</v>
       </c>
       <c r="U153" t="s" s="2">
         <v>75</v>
@@ -19976,7 +19990,7 @@
       </c>
       <c r="Z153" s="2"/>
       <c r="AA153" t="s" s="2">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="AB153" t="s" s="2">
         <v>75</v>
@@ -20014,7 +20028,7 @@
         <v>386</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="C154" t="s" s="2">
         <v>573</v>
@@ -20117,7 +20131,7 @@
         <v>386</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="C155" t="s" s="2">
         <v>575</v>
@@ -20222,7 +20236,7 @@
         <v>386</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="C156" t="s" s="2">
         <v>577</v>
@@ -20329,7 +20343,7 @@
         <v>386</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="C157" t="s" s="2">
         <v>579</v>
@@ -20432,7 +20446,7 @@
         <v>386</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="C158" t="s" s="2">
         <v>581</v>
@@ -20537,7 +20551,7 @@
         <v>386</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="C159" t="s" s="2">
         <v>583</v>
@@ -20644,7 +20658,7 @@
         <v>386</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="C160" t="s" s="2">
         <v>585</v>
@@ -20749,7 +20763,7 @@
         <v>386</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="C161" t="s" s="2">
         <v>587</v>
@@ -20854,7 +20868,7 @@
         <v>386</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="C162" t="s" s="2">
         <v>589</v>
@@ -20959,7 +20973,7 @@
         <v>386</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="C163" t="s" s="2">
         <v>591</v>
@@ -21066,7 +21080,7 @@
         <v>386</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="C164" t="s" s="2">
         <v>593</v>
@@ -21173,10 +21187,10 @@
         <v>386</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="C165" t="s" s="2">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="D165" s="2"/>
       <c r="E165" t="s" s="2">
@@ -21202,13 +21216,13 @@
         <v>177</v>
       </c>
       <c r="M165" t="s" s="2">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="N165" t="s" s="2">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="O165" t="s" s="2">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="P165" s="2"/>
       <c r="Q165" t="s" s="2">
@@ -21258,7 +21272,7 @@
         <v>75</v>
       </c>
       <c r="AG165" t="s" s="2">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="AH165" t="s" s="2">
         <v>76</v>
@@ -21278,10 +21292,10 @@
         <v>386</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="C166" t="s" s="2">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="D166" s="2"/>
       <c r="E166" t="s" s="2">
@@ -21381,10 +21395,10 @@
         <v>386</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="C167" t="s" s="2">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="D167" s="2"/>
       <c r="E167" t="s" s="2">
@@ -21486,10 +21500,10 @@
         <v>386</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="C168" t="s" s="2">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="D168" s="2"/>
       <c r="E168" t="s" s="2">
@@ -21591,10 +21605,10 @@
         <v>386</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="C169" t="s" s="2">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="D169" s="2"/>
       <c r="E169" t="s" s="2">
@@ -21696,10 +21710,10 @@
         <v>386</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="C170" t="s" s="2">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="D170" s="2"/>
       <c r="E170" t="s" s="2">
@@ -21801,10 +21815,10 @@
         <v>386</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="C171" t="s" s="2">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="D171" s="2"/>
       <c r="E171" t="s" s="2">
@@ -21904,10 +21918,10 @@
         <v>386</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="C172" t="s" s="2">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="D172" s="2"/>
       <c r="E172" t="s" s="2">
@@ -22009,10 +22023,10 @@
         <v>386</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="C173" t="s" s="2">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="D173" s="2"/>
       <c r="E173" t="s" s="2">
@@ -22038,16 +22052,16 @@
         <v>104</v>
       </c>
       <c r="M173" t="s" s="2">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="N173" t="s" s="2">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="O173" t="s" s="2">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="P173" t="s" s="2">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="Q173" t="s" s="2">
         <v>75</v>
@@ -22075,10 +22089,10 @@
         <v>152</v>
       </c>
       <c r="Z173" t="s" s="2">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="AA173" t="s" s="2">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="AB173" t="s" s="2">
         <v>75</v>
@@ -22096,7 +22110,7 @@
         <v>75</v>
       </c>
       <c r="AG173" t="s" s="2">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="AH173" t="s" s="2">
         <v>76</v>
@@ -22116,10 +22130,10 @@
         <v>386</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="C174" t="s" s="2">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="D174" s="2"/>
       <c r="E174" t="s" s="2">
@@ -22145,16 +22159,16 @@
         <v>162</v>
       </c>
       <c r="M174" t="s" s="2">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="N174" t="s" s="2">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="O174" t="s" s="2">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="P174" t="s" s="2">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="Q174" t="s" s="2">
         <v>75</v>
@@ -22182,10 +22196,10 @@
         <v>201</v>
       </c>
       <c r="Z174" t="s" s="2">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="AA174" t="s" s="2">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="AB174" t="s" s="2">
         <v>75</v>
@@ -22203,7 +22217,7 @@
         <v>75</v>
       </c>
       <c r="AG174" t="s" s="2">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="AH174" t="s" s="2">
         <v>76</v>
@@ -22223,10 +22237,10 @@
         <v>386</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="C175" t="s" s="2">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="D175" s="2"/>
       <c r="E175" t="s" s="2">
@@ -22252,16 +22266,16 @@
         <v>98</v>
       </c>
       <c r="M175" t="s" s="2">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="N175" t="s" s="2">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="O175" t="s" s="2">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="P175" t="s" s="2">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="Q175" t="s" s="2">
         <v>75</v>
@@ -22274,7 +22288,7 @@
         <v>75</v>
       </c>
       <c r="U175" t="s" s="2">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="V175" t="s" s="2">
         <v>75</v>
@@ -22310,7 +22324,7 @@
         <v>75</v>
       </c>
       <c r="AG175" t="s" s="2">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="AH175" t="s" s="2">
         <v>76</v>
@@ -22330,10 +22344,10 @@
         <v>386</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="C176" t="s" s="2">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="D176" s="2"/>
       <c r="E176" t="s" s="2">
@@ -22359,13 +22373,13 @@
         <v>181</v>
       </c>
       <c r="M176" t="s" s="2">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="N176" t="s" s="2">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="O176" t="s" s="2">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="P176" s="2"/>
       <c r="Q176" t="s" s="2">
@@ -22379,7 +22393,7 @@
         <v>75</v>
       </c>
       <c r="U176" t="s" s="2">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="V176" t="s" s="2">
         <v>75</v>
@@ -22415,7 +22429,7 @@
         <v>75</v>
       </c>
       <c r="AG176" t="s" s="2">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="AH176" t="s" s="2">
         <v>76</v>
@@ -22435,10 +22449,10 @@
         <v>386</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="C177" t="s" s="2">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="D177" s="2"/>
       <c r="E177" t="s" s="2">
@@ -22464,10 +22478,10 @@
         <v>362</v>
       </c>
       <c r="M177" t="s" s="2">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="N177" t="s" s="2">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="O177" s="2"/>
       <c r="P177" s="2"/>
@@ -22518,7 +22532,7 @@
         <v>75</v>
       </c>
       <c r="AG177" t="s" s="2">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="AH177" t="s" s="2">
         <v>76</v>
@@ -22538,10 +22552,10 @@
         <v>386</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="C178" t="s" s="2">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="D178" s="2"/>
       <c r="E178" t="s" s="2">
@@ -22567,13 +22581,13 @@
         <v>232</v>
       </c>
       <c r="M178" t="s" s="2">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="N178" t="s" s="2">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="O178" t="s" s="2">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="P178" s="2"/>
       <c r="Q178" t="s" s="2">
@@ -22623,7 +22637,7 @@
         <v>75</v>
       </c>
       <c r="AG178" t="s" s="2">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="AH178" t="s" s="2">
         <v>76</v>
@@ -22643,10 +22657,10 @@
         <v>386</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="C179" t="s" s="2">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="D179" s="2"/>
       <c r="E179" t="s" s="2">
@@ -22748,10 +22762,10 @@
         <v>386</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="C180" t="s" s="2">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="D180" s="2"/>
       <c r="E180" t="s" s="2">
@@ -22777,13 +22791,13 @@
         <v>332</v>
       </c>
       <c r="M180" t="s" s="2">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="N180" t="s" s="2">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="O180" t="s" s="2">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="P180" s="2"/>
       <c r="Q180" t="s" s="2">
@@ -22833,7 +22847,7 @@
         <v>75</v>
       </c>
       <c r="AG180" t="s" s="2">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="AH180" t="s" s="2">
         <v>76</v>
@@ -22853,14 +22867,14 @@
         <v>386</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="C181" t="s" s="2">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="D181" s="2"/>
       <c r="E181" t="s" s="2">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="F181" s="2"/>
       <c r="G181" t="s" s="2">
@@ -22879,16 +22893,16 @@
         <v>85</v>
       </c>
       <c r="L181" t="s" s="2">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="M181" t="s" s="2">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="N181" t="s" s="2">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="O181" t="s" s="2">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="P181" s="2"/>
       <c r="Q181" t="s" s="2">
@@ -22938,7 +22952,7 @@
         <v>75</v>
       </c>
       <c r="AG181" t="s" s="2">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="AH181" t="s" s="2">
         <v>76</v>
@@ -22958,14 +22972,14 @@
         <v>386</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="C182" t="s" s="2">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="D182" s="2"/>
       <c r="E182" t="s" s="2">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="F182" s="2"/>
       <c r="G182" t="s" s="2">
@@ -22987,10 +23001,10 @@
         <v>232</v>
       </c>
       <c r="M182" t="s" s="2">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="N182" t="s" s="2">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="O182" s="2"/>
       <c r="P182" s="2"/>
@@ -23041,7 +23055,7 @@
         <v>75</v>
       </c>
       <c r="AG182" t="s" s="2">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="AH182" t="s" s="2">
         <v>76</v>
@@ -23061,10 +23075,10 @@
         <v>386</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="C183" t="s" s="2">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="D183" s="2"/>
       <c r="E183" t="s" s="2">
@@ -23087,16 +23101,16 @@
         <v>85</v>
       </c>
       <c r="L183" t="s" s="2">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="M183" t="s" s="2">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="N183" t="s" s="2">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="O183" t="s" s="2">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="P183" s="2"/>
       <c r="Q183" t="s" s="2">
@@ -23146,7 +23160,7 @@
         <v>75</v>
       </c>
       <c r="AG183" t="s" s="2">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="AH183" t="s" s="2">
         <v>76</v>
@@ -23166,10 +23180,10 @@
         <v>386</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="C184" t="s" s="2">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="D184" s="2"/>
       <c r="E184" t="s" s="2">
@@ -23269,10 +23283,10 @@
         <v>386</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="C185" t="s" s="2">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="D185" s="2"/>
       <c r="E185" t="s" s="2">
@@ -23374,10 +23388,10 @@
         <v>386</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="C186" t="s" s="2">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="D186" s="2"/>
       <c r="E186" t="s" s="2">
@@ -23479,10 +23493,10 @@
         <v>386</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="C187" t="s" s="2">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="D187" s="2"/>
       <c r="E187" t="s" s="2">
@@ -23584,10 +23598,10 @@
         <v>386</v>
       </c>
       <c r="B188" t="s" s="2">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="C188" t="s" s="2">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="D188" s="2"/>
       <c r="E188" t="s" s="2">
@@ -23689,10 +23703,10 @@
         <v>386</v>
       </c>
       <c r="B189" t="s" s="2">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="C189" t="s" s="2">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="D189" s="2"/>
       <c r="E189" t="s" s="2">
@@ -23794,10 +23808,10 @@
         <v>386</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="C190" t="s" s="2">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="D190" s="2"/>
       <c r="E190" t="s" s="2">
@@ -23823,10 +23837,10 @@
         <v>237</v>
       </c>
       <c r="M190" t="s" s="2">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="N190" t="s" s="2">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="O190" s="2"/>
       <c r="P190" s="2"/>
@@ -23877,7 +23891,7 @@
         <v>75</v>
       </c>
       <c r="AG190" t="s" s="2">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="AH190" t="s" s="2">
         <v>76</v>
@@ -23897,10 +23911,10 @@
         <v>386</v>
       </c>
       <c r="B191" t="s" s="2">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="C191" t="s" s="2">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D191" s="2"/>
       <c r="E191" t="s" s="2">
@@ -24000,10 +24014,10 @@
         <v>386</v>
       </c>
       <c r="B192" t="s" s="2">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="C192" t="s" s="2">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="D192" s="2"/>
       <c r="E192" t="s" s="2">
@@ -24105,10 +24119,10 @@
         <v>386</v>
       </c>
       <c r="B193" t="s" s="2">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="C193" t="s" s="2">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="D193" s="2"/>
       <c r="E193" t="s" s="2">
@@ -24212,10 +24226,10 @@
         <v>386</v>
       </c>
       <c r="B194" t="s" s="2">
-        <v>716</v>
+        <v>718</v>
       </c>
       <c r="C194" t="s" s="2">
-        <v>716</v>
+        <v>718</v>
       </c>
       <c r="D194" s="2"/>
       <c r="E194" t="s" s="2">
@@ -24241,10 +24255,10 @@
         <v>98</v>
       </c>
       <c r="M194" t="s" s="2">
-        <v>717</v>
+        <v>719</v>
       </c>
       <c r="N194" t="s" s="2">
-        <v>718</v>
+        <v>720</v>
       </c>
       <c r="O194" s="2"/>
       <c r="P194" s="2"/>
@@ -24295,7 +24309,7 @@
         <v>75</v>
       </c>
       <c r="AG194" t="s" s="2">
-        <v>716</v>
+        <v>718</v>
       </c>
       <c r="AH194" t="s" s="2">
         <v>76</v>
@@ -24304,7 +24318,7 @@
         <v>84</v>
       </c>
       <c r="AJ194" t="s" s="2">
-        <v>719</v>
+        <v>721</v>
       </c>
       <c r="AK194" t="s" s="2">
         <v>96</v>
@@ -24315,10 +24329,10 @@
         <v>386</v>
       </c>
       <c r="B195" t="s" s="2">
-        <v>720</v>
+        <v>722</v>
       </c>
       <c r="C195" t="s" s="2">
-        <v>720</v>
+        <v>722</v>
       </c>
       <c r="D195" s="2"/>
       <c r="E195" t="s" s="2">
@@ -24344,13 +24358,13 @@
         <v>98</v>
       </c>
       <c r="M195" t="s" s="2">
-        <v>721</v>
+        <v>723</v>
       </c>
       <c r="N195" t="s" s="2">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="O195" t="s" s="2">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="P195" s="2"/>
       <c r="Q195" t="s" s="2">
@@ -24400,7 +24414,7 @@
         <v>75</v>
       </c>
       <c r="AG195" t="s" s="2">
-        <v>720</v>
+        <v>722</v>
       </c>
       <c r="AH195" t="s" s="2">
         <v>76</v>
@@ -24409,7 +24423,7 @@
         <v>84</v>
       </c>
       <c r="AJ195" t="s" s="2">
-        <v>719</v>
+        <v>721</v>
       </c>
       <c r="AK195" t="s" s="2">
         <v>96</v>
@@ -24420,10 +24434,10 @@
         <v>386</v>
       </c>
       <c r="B196" t="s" s="2">
-        <v>723</v>
+        <v>725</v>
       </c>
       <c r="C196" t="s" s="2">
-        <v>723</v>
+        <v>725</v>
       </c>
       <c r="D196" s="2"/>
       <c r="E196" t="s" s="2">
@@ -24449,16 +24463,16 @@
         <v>162</v>
       </c>
       <c r="M196" t="s" s="2">
-        <v>724</v>
+        <v>726</v>
       </c>
       <c r="N196" t="s" s="2">
-        <v>725</v>
+        <v>727</v>
       </c>
       <c r="O196" t="s" s="2">
-        <v>726</v>
+        <v>728</v>
       </c>
       <c r="P196" t="s" s="2">
-        <v>727</v>
+        <v>729</v>
       </c>
       <c r="Q196" t="s" s="2">
         <v>75</v>
@@ -24486,10 +24500,10 @@
         <v>201</v>
       </c>
       <c r="Z196" t="s" s="2">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="AA196" t="s" s="2">
-        <v>729</v>
+        <v>731</v>
       </c>
       <c r="AB196" t="s" s="2">
         <v>75</v>
@@ -24507,7 +24521,7 @@
         <v>75</v>
       </c>
       <c r="AG196" t="s" s="2">
-        <v>723</v>
+        <v>725</v>
       </c>
       <c r="AH196" t="s" s="2">
         <v>76</v>
@@ -24516,7 +24530,7 @@
         <v>84</v>
       </c>
       <c r="AJ196" t="s" s="2">
-        <v>719</v>
+        <v>721</v>
       </c>
       <c r="AK196" t="s" s="2">
         <v>96</v>
@@ -24527,10 +24541,10 @@
         <v>386</v>
       </c>
       <c r="B197" t="s" s="2">
-        <v>730</v>
+        <v>732</v>
       </c>
       <c r="C197" t="s" s="2">
-        <v>730</v>
+        <v>732</v>
       </c>
       <c r="D197" s="2"/>
       <c r="E197" t="s" s="2">
@@ -24630,10 +24644,10 @@
         <v>386</v>
       </c>
       <c r="B198" t="s" s="2">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="C198" t="s" s="2">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="D198" s="2"/>
       <c r="E198" t="s" s="2">
@@ -24733,13 +24747,13 @@
         <v>386</v>
       </c>
       <c r="B199" t="s" s="2">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="C199" t="s" s="2">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="D199" t="s" s="2">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="E199" t="s" s="2">
         <v>75</v>
@@ -24761,7 +24775,7 @@
         <v>75</v>
       </c>
       <c r="L199" t="s" s="2">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="M199" t="s" s="2">
         <v>445</v>
@@ -24838,10 +24852,10 @@
         <v>386</v>
       </c>
       <c r="B200" t="s" s="2">
-        <v>735</v>
+        <v>737</v>
       </c>
       <c r="C200" t="s" s="2">
-        <v>735</v>
+        <v>737</v>
       </c>
       <c r="D200" s="2"/>
       <c r="E200" t="s" s="2">
@@ -24945,10 +24959,10 @@
         <v>386</v>
       </c>
       <c r="B201" t="s" s="2">
-        <v>736</v>
+        <v>738</v>
       </c>
       <c r="C201" t="s" s="2">
-        <v>736</v>
+        <v>738</v>
       </c>
       <c r="D201" s="2"/>
       <c r="E201" t="s" s="2">
@@ -25052,10 +25066,10 @@
         <v>386</v>
       </c>
       <c r="B202" t="s" s="2">
-        <v>737</v>
+        <v>739</v>
       </c>
       <c r="C202" t="s" s="2">
-        <v>737</v>
+        <v>739</v>
       </c>
       <c r="D202" s="2"/>
       <c r="E202" t="s" s="2">
@@ -25081,10 +25095,10 @@
         <v>237</v>
       </c>
       <c r="M202" t="s" s="2">
-        <v>738</v>
+        <v>740</v>
       </c>
       <c r="N202" t="s" s="2">
-        <v>739</v>
+        <v>741</v>
       </c>
       <c r="O202" s="2"/>
       <c r="P202" s="2"/>
@@ -25135,7 +25149,7 @@
         <v>75</v>
       </c>
       <c r="AG202" t="s" s="2">
-        <v>737</v>
+        <v>739</v>
       </c>
       <c r="AH202" t="s" s="2">
         <v>76</v>
@@ -25155,10 +25169,10 @@
         <v>386</v>
       </c>
       <c r="B203" t="s" s="2">
-        <v>740</v>
+        <v>742</v>
       </c>
       <c r="C203" t="s" s="2">
-        <v>740</v>
+        <v>742</v>
       </c>
       <c r="D203" s="2"/>
       <c r="E203" t="s" s="2">
@@ -25258,10 +25272,10 @@
         <v>386</v>
       </c>
       <c r="B204" t="s" s="2">
-        <v>741</v>
+        <v>743</v>
       </c>
       <c r="C204" t="s" s="2">
-        <v>741</v>
+        <v>743</v>
       </c>
       <c r="D204" s="2"/>
       <c r="E204" t="s" s="2">
@@ -25363,10 +25377,10 @@
         <v>386</v>
       </c>
       <c r="B205" t="s" s="2">
-        <v>742</v>
+        <v>744</v>
       </c>
       <c r="C205" t="s" s="2">
-        <v>742</v>
+        <v>744</v>
       </c>
       <c r="D205" s="2"/>
       <c r="E205" t="s" s="2">
@@ -25470,10 +25484,10 @@
         <v>386</v>
       </c>
       <c r="B206" t="s" s="2">
-        <v>743</v>
+        <v>745</v>
       </c>
       <c r="C206" t="s" s="2">
-        <v>743</v>
+        <v>745</v>
       </c>
       <c r="D206" s="2"/>
       <c r="E206" t="s" s="2">
@@ -25499,10 +25513,10 @@
         <v>508</v>
       </c>
       <c r="M206" t="s" s="2">
-        <v>744</v>
+        <v>746</v>
       </c>
       <c r="N206" t="s" s="2">
-        <v>745</v>
+        <v>747</v>
       </c>
       <c r="O206" s="2"/>
       <c r="P206" s="2"/>
@@ -25553,7 +25567,7 @@
         <v>75</v>
       </c>
       <c r="AG206" t="s" s="2">
-        <v>743</v>
+        <v>745</v>
       </c>
       <c r="AH206" t="s" s="2">
         <v>84</v>
@@ -25573,10 +25587,10 @@
         <v>386</v>
       </c>
       <c r="B207" t="s" s="2">
-        <v>746</v>
+        <v>748</v>
       </c>
       <c r="C207" t="s" s="2">
-        <v>746</v>
+        <v>748</v>
       </c>
       <c r="D207" s="2"/>
       <c r="E207" t="s" s="2">
@@ -25599,13 +25613,13 @@
         <v>75</v>
       </c>
       <c r="L207" t="s" s="2">
-        <v>747</v>
+        <v>749</v>
       </c>
       <c r="M207" t="s" s="2">
-        <v>748</v>
+        <v>750</v>
       </c>
       <c r="N207" t="s" s="2">
-        <v>749</v>
+        <v>751</v>
       </c>
       <c r="O207" s="2"/>
       <c r="P207" s="2"/>
@@ -25656,7 +25670,7 @@
         <v>75</v>
       </c>
       <c r="AG207" t="s" s="2">
-        <v>746</v>
+        <v>748</v>
       </c>
       <c r="AH207" t="s" s="2">
         <v>76</v>
@@ -25676,10 +25690,10 @@
         <v>386</v>
       </c>
       <c r="B208" t="s" s="2">
-        <v>750</v>
+        <v>752</v>
       </c>
       <c r="C208" t="s" s="2">
-        <v>750</v>
+        <v>752</v>
       </c>
       <c r="D208" s="2"/>
       <c r="E208" t="s" s="2">
@@ -25705,10 +25719,10 @@
         <v>332</v>
       </c>
       <c r="M208" t="s" s="2">
-        <v>751</v>
+        <v>753</v>
       </c>
       <c r="N208" t="s" s="2">
-        <v>752</v>
+        <v>754</v>
       </c>
       <c r="O208" s="2"/>
       <c r="P208" s="2"/>
@@ -25759,7 +25773,7 @@
         <v>75</v>
       </c>
       <c r="AG208" t="s" s="2">
-        <v>750</v>
+        <v>752</v>
       </c>
       <c r="AH208" t="s" s="2">
         <v>76</v>
@@ -25779,10 +25793,10 @@
         <v>386</v>
       </c>
       <c r="B209" t="s" s="2">
-        <v>753</v>
+        <v>755</v>
       </c>
       <c r="C209" t="s" s="2">
-        <v>753</v>
+        <v>755</v>
       </c>
       <c r="D209" s="2"/>
       <c r="E209" t="s" s="2">
@@ -25808,10 +25822,10 @@
         <v>237</v>
       </c>
       <c r="M209" t="s" s="2">
-        <v>754</v>
+        <v>756</v>
       </c>
       <c r="N209" t="s" s="2">
-        <v>755</v>
+        <v>757</v>
       </c>
       <c r="O209" s="2"/>
       <c r="P209" s="2"/>
@@ -25862,7 +25876,7 @@
         <v>75</v>
       </c>
       <c r="AG209" t="s" s="2">
-        <v>753</v>
+        <v>755</v>
       </c>
       <c r="AH209" t="s" s="2">
         <v>76</v>
@@ -25882,10 +25896,10 @@
         <v>386</v>
       </c>
       <c r="B210" t="s" s="2">
-        <v>756</v>
+        <v>758</v>
       </c>
       <c r="C210" t="s" s="2">
-        <v>756</v>
+        <v>758</v>
       </c>
       <c r="D210" s="2"/>
       <c r="E210" t="s" s="2">
@@ -25985,10 +25999,10 @@
         <v>386</v>
       </c>
       <c r="B211" t="s" s="2">
-        <v>757</v>
+        <v>759</v>
       </c>
       <c r="C211" t="s" s="2">
-        <v>757</v>
+        <v>759</v>
       </c>
       <c r="D211" s="2"/>
       <c r="E211" t="s" s="2">
@@ -26090,10 +26104,10 @@
         <v>386</v>
       </c>
       <c r="B212" t="s" s="2">
-        <v>758</v>
+        <v>760</v>
       </c>
       <c r="C212" t="s" s="2">
-        <v>758</v>
+        <v>760</v>
       </c>
       <c r="D212" s="2"/>
       <c r="E212" t="s" s="2">
@@ -26197,10 +26211,10 @@
         <v>386</v>
       </c>
       <c r="B213" t="s" s="2">
-        <v>759</v>
+        <v>761</v>
       </c>
       <c r="C213" t="s" s="2">
-        <v>759</v>
+        <v>761</v>
       </c>
       <c r="D213" s="2"/>
       <c r="E213" t="s" s="2">
@@ -26226,10 +26240,10 @@
         <v>104</v>
       </c>
       <c r="M213" t="s" s="2">
-        <v>760</v>
+        <v>762</v>
       </c>
       <c r="N213" t="s" s="2">
-        <v>761</v>
+        <v>763</v>
       </c>
       <c r="O213" s="2"/>
       <c r="P213" s="2"/>
@@ -26259,10 +26273,10 @@
         <v>152</v>
       </c>
       <c r="Z213" t="s" s="2">
-        <v>762</v>
+        <v>764</v>
       </c>
       <c r="AA213" t="s" s="2">
-        <v>763</v>
+        <v>765</v>
       </c>
       <c r="AB213" t="s" s="2">
         <v>75</v>
@@ -26280,7 +26294,7 @@
         <v>75</v>
       </c>
       <c r="AG213" t="s" s="2">
-        <v>759</v>
+        <v>761</v>
       </c>
       <c r="AH213" t="s" s="2">
         <v>76</v>
@@ -26300,10 +26314,10 @@
         <v>386</v>
       </c>
       <c r="B214" t="s" s="2">
-        <v>764</v>
+        <v>766</v>
       </c>
       <c r="C214" t="s" s="2">
-        <v>764</v>
+        <v>766</v>
       </c>
       <c r="D214" s="2"/>
       <c r="E214" t="s" s="2">
@@ -26329,10 +26343,10 @@
         <v>362</v>
       </c>
       <c r="M214" t="s" s="2">
-        <v>765</v>
+        <v>767</v>
       </c>
       <c r="N214" t="s" s="2">
-        <v>766</v>
+        <v>768</v>
       </c>
       <c r="O214" s="2"/>
       <c r="P214" s="2"/>
@@ -26383,7 +26397,7 @@
         <v>75</v>
       </c>
       <c r="AG214" t="s" s="2">
-        <v>764</v>
+        <v>766</v>
       </c>
       <c r="AH214" t="s" s="2">
         <v>76</v>
@@ -26403,10 +26417,10 @@
         <v>386</v>
       </c>
       <c r="B215" t="s" s="2">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="C215" t="s" s="2">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="D215" s="2"/>
       <c r="E215" t="s" s="2">
@@ -26506,10 +26520,10 @@
         <v>386</v>
       </c>
       <c r="B216" t="s" s="2">
-        <v>768</v>
+        <v>770</v>
       </c>
       <c r="C216" t="s" s="2">
-        <v>768</v>
+        <v>770</v>
       </c>
       <c r="D216" s="2"/>
       <c r="E216" t="s" s="2">
@@ -26611,10 +26625,10 @@
         <v>386</v>
       </c>
       <c r="B217" t="s" s="2">
-        <v>769</v>
+        <v>771</v>
       </c>
       <c r="C217" t="s" s="2">
-        <v>769</v>
+        <v>771</v>
       </c>
       <c r="D217" s="2"/>
       <c r="E217" t="s" s="2">
@@ -26640,13 +26654,13 @@
         <v>332</v>
       </c>
       <c r="M217" t="s" s="2">
-        <v>770</v>
+        <v>772</v>
       </c>
       <c r="N217" t="s" s="2">
-        <v>771</v>
+        <v>773</v>
       </c>
       <c r="O217" t="s" s="2">
-        <v>772</v>
+        <v>774</v>
       </c>
       <c r="P217" s="2"/>
       <c r="Q217" t="s" s="2">
@@ -26696,7 +26710,7 @@
         <v>75</v>
       </c>
       <c r="AG217" t="s" s="2">
-        <v>773</v>
+        <v>775</v>
       </c>
       <c r="AH217" t="s" s="2">
         <v>76</v>
@@ -26705,7 +26719,7 @@
         <v>84</v>
       </c>
       <c r="AJ217" t="s" s="2">
-        <v>774</v>
+        <v>776</v>
       </c>
       <c r="AK217" t="s" s="2">
         <v>96</v>
@@ -26716,10 +26730,10 @@
         <v>386</v>
       </c>
       <c r="B218" t="s" s="2">
-        <v>775</v>
+        <v>777</v>
       </c>
       <c r="C218" t="s" s="2">
-        <v>775</v>
+        <v>777</v>
       </c>
       <c r="D218" s="2"/>
       <c r="E218" t="s" s="2">
@@ -26745,20 +26759,20 @@
         <v>332</v>
       </c>
       <c r="M218" t="s" s="2">
-        <v>776</v>
+        <v>778</v>
       </c>
       <c r="N218" t="s" s="2">
-        <v>777</v>
+        <v>779</v>
       </c>
       <c r="O218" t="s" s="2">
-        <v>778</v>
+        <v>780</v>
       </c>
       <c r="P218" s="2"/>
       <c r="Q218" t="s" s="2">
         <v>75</v>
       </c>
       <c r="R218" t="s" s="2">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="S218" t="s" s="2">
         <v>75</v>
@@ -26803,7 +26817,7 @@
         <v>75</v>
       </c>
       <c r="AG218" t="s" s="2">
-        <v>780</v>
+        <v>782</v>
       </c>
       <c r="AH218" t="s" s="2">
         <v>76</v>
@@ -26812,7 +26826,7 @@
         <v>84</v>
       </c>
       <c r="AJ218" t="s" s="2">
-        <v>774</v>
+        <v>776</v>
       </c>
       <c r="AK218" t="s" s="2">
         <v>96</v>
@@ -26823,10 +26837,10 @@
         <v>386</v>
       </c>
       <c r="B219" t="s" s="2">
-        <v>781</v>
+        <v>783</v>
       </c>
       <c r="C219" t="s" s="2">
-        <v>781</v>
+        <v>783</v>
       </c>
       <c r="D219" s="2"/>
       <c r="E219" t="s" s="2">
@@ -26852,10 +26866,10 @@
         <v>237</v>
       </c>
       <c r="M219" t="s" s="2">
-        <v>782</v>
+        <v>784</v>
       </c>
       <c r="N219" t="s" s="2">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="O219" s="2"/>
       <c r="P219" s="2"/>
@@ -26863,7 +26877,7 @@
         <v>75</v>
       </c>
       <c r="R219" t="s" s="2">
-        <v>784</v>
+        <v>786</v>
       </c>
       <c r="S219" t="s" s="2">
         <v>75</v>
@@ -26908,7 +26922,7 @@
         <v>75</v>
       </c>
       <c r="AG219" t="s" s="2">
-        <v>781</v>
+        <v>783</v>
       </c>
       <c r="AH219" t="s" s="2">
         <v>76</v>
@@ -26928,10 +26942,10 @@
         <v>386</v>
       </c>
       <c r="B220" t="s" s="2">
-        <v>785</v>
+        <v>787</v>
       </c>
       <c r="C220" t="s" s="2">
-        <v>785</v>
+        <v>787</v>
       </c>
       <c r="D220" s="2"/>
       <c r="E220" t="s" s="2">
@@ -27031,10 +27045,10 @@
         <v>386</v>
       </c>
       <c r="B221" t="s" s="2">
-        <v>786</v>
+        <v>788</v>
       </c>
       <c r="C221" t="s" s="2">
-        <v>786</v>
+        <v>788</v>
       </c>
       <c r="D221" s="2"/>
       <c r="E221" t="s" s="2">
@@ -27136,10 +27150,10 @@
         <v>386</v>
       </c>
       <c r="B222" t="s" s="2">
-        <v>787</v>
+        <v>789</v>
       </c>
       <c r="C222" t="s" s="2">
-        <v>787</v>
+        <v>789</v>
       </c>
       <c r="D222" s="2"/>
       <c r="E222" t="s" s="2">
@@ -27243,10 +27257,10 @@
         <v>386</v>
       </c>
       <c r="B223" t="s" s="2">
-        <v>788</v>
+        <v>790</v>
       </c>
       <c r="C223" t="s" s="2">
-        <v>788</v>
+        <v>790</v>
       </c>
       <c r="D223" s="2"/>
       <c r="E223" t="s" s="2">
@@ -27272,10 +27286,10 @@
         <v>162</v>
       </c>
       <c r="M223" t="s" s="2">
-        <v>789</v>
+        <v>791</v>
       </c>
       <c r="N223" t="s" s="2">
-        <v>790</v>
+        <v>792</v>
       </c>
       <c r="O223" s="2"/>
       <c r="P223" s="2"/>
@@ -27305,10 +27319,10 @@
         <v>201</v>
       </c>
       <c r="Z223" t="s" s="2">
-        <v>791</v>
+        <v>793</v>
       </c>
       <c r="AA223" t="s" s="2">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="AB223" t="s" s="2">
         <v>75</v>
@@ -27326,7 +27340,7 @@
         <v>75</v>
       </c>
       <c r="AG223" t="s" s="2">
-        <v>788</v>
+        <v>790</v>
       </c>
       <c r="AH223" t="s" s="2">
         <v>84</v>
@@ -27346,10 +27360,10 @@
         <v>386</v>
       </c>
       <c r="B224" t="s" s="2">
-        <v>793</v>
+        <v>795</v>
       </c>
       <c r="C224" t="s" s="2">
-        <v>793</v>
+        <v>795</v>
       </c>
       <c r="D224" s="2"/>
       <c r="E224" t="s" s="2">
@@ -27372,13 +27386,13 @@
         <v>75</v>
       </c>
       <c r="L224" t="s" s="2">
-        <v>794</v>
+        <v>796</v>
       </c>
       <c r="M224" t="s" s="2">
-        <v>795</v>
+        <v>797</v>
       </c>
       <c r="N224" t="s" s="2">
-        <v>796</v>
+        <v>798</v>
       </c>
       <c r="O224" s="2"/>
       <c r="P224" s="2"/>
@@ -27429,7 +27443,7 @@
         <v>75</v>
       </c>
       <c r="AG224" t="s" s="2">
-        <v>793</v>
+        <v>795</v>
       </c>
       <c r="AH224" t="s" s="2">
         <v>84</v>
@@ -27449,10 +27463,10 @@
         <v>386</v>
       </c>
       <c r="B225" t="s" s="2">
-        <v>797</v>
+        <v>799</v>
       </c>
       <c r="C225" t="s" s="2">
-        <v>797</v>
+        <v>799</v>
       </c>
       <c r="D225" s="2"/>
       <c r="E225" t="s" s="2">
@@ -27478,20 +27492,20 @@
         <v>162</v>
       </c>
       <c r="M225" t="s" s="2">
-        <v>798</v>
+        <v>800</v>
       </c>
       <c r="N225" t="s" s="2">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="O225" t="s" s="2">
-        <v>800</v>
+        <v>802</v>
       </c>
       <c r="P225" s="2"/>
       <c r="Q225" t="s" s="2">
         <v>75</v>
       </c>
       <c r="R225" t="s" s="2">
-        <v>801</v>
+        <v>803</v>
       </c>
       <c r="S225" t="s" s="2">
         <v>75</v>
@@ -27515,10 +27529,10 @@
         <v>173</v>
       </c>
       <c r="Z225" t="s" s="2">
-        <v>802</v>
+        <v>804</v>
       </c>
       <c r="AA225" t="s" s="2">
-        <v>803</v>
+        <v>805</v>
       </c>
       <c r="AB225" t="s" s="2">
         <v>75</v>
@@ -27536,7 +27550,7 @@
         <v>75</v>
       </c>
       <c r="AG225" t="s" s="2">
-        <v>797</v>
+        <v>799</v>
       </c>
       <c r="AH225" t="s" s="2">
         <v>76</v>
@@ -27556,10 +27570,10 @@
         <v>386</v>
       </c>
       <c r="B226" t="s" s="2">
-        <v>804</v>
+        <v>806</v>
       </c>
       <c r="C226" t="s" s="2">
-        <v>804</v>
+        <v>806</v>
       </c>
       <c r="D226" s="2"/>
       <c r="E226" t="s" s="2">
@@ -27585,13 +27599,13 @@
         <v>338</v>
       </c>
       <c r="M226" t="s" s="2">
-        <v>805</v>
+        <v>807</v>
       </c>
       <c r="N226" t="s" s="2">
-        <v>806</v>
+        <v>808</v>
       </c>
       <c r="O226" t="s" s="2">
-        <v>807</v>
+        <v>809</v>
       </c>
       <c r="P226" s="2"/>
       <c r="Q226" t="s" s="2">
@@ -27641,7 +27655,7 @@
         <v>75</v>
       </c>
       <c r="AG226" t="s" s="2">
-        <v>804</v>
+        <v>806</v>
       </c>
       <c r="AH226" t="s" s="2">
         <v>76</v>
@@ -27661,10 +27675,10 @@
         <v>386</v>
       </c>
       <c r="B227" t="s" s="2">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="C227" t="s" s="2">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="D227" s="2"/>
       <c r="E227" t="s" s="2">
@@ -27690,13 +27704,13 @@
         <v>338</v>
       </c>
       <c r="M227" t="s" s="2">
-        <v>809</v>
+        <v>811</v>
       </c>
       <c r="N227" t="s" s="2">
-        <v>810</v>
+        <v>812</v>
       </c>
       <c r="O227" t="s" s="2">
-        <v>811</v>
+        <v>813</v>
       </c>
       <c r="P227" s="2"/>
       <c r="Q227" t="s" s="2">
@@ -27725,10 +27739,10 @@
         <v>201</v>
       </c>
       <c r="Z227" t="s" s="2">
-        <v>812</v>
+        <v>814</v>
       </c>
       <c r="AA227" t="s" s="2">
-        <v>813</v>
+        <v>815</v>
       </c>
       <c r="AB227" t="s" s="2">
         <v>75</v>
@@ -27746,7 +27760,7 @@
         <v>75</v>
       </c>
       <c r="AG227" t="s" s="2">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="AH227" t="s" s="2">
         <v>76</v>
@@ -27766,10 +27780,10 @@
         <v>386</v>
       </c>
       <c r="B228" t="s" s="2">
-        <v>814</v>
+        <v>816</v>
       </c>
       <c r="C228" t="s" s="2">
-        <v>814</v>
+        <v>816</v>
       </c>
       <c r="D228" s="2"/>
       <c r="E228" t="s" s="2">
@@ -27795,13 +27809,13 @@
         <v>338</v>
       </c>
       <c r="M228" t="s" s="2">
-        <v>815</v>
+        <v>817</v>
       </c>
       <c r="N228" t="s" s="2">
-        <v>816</v>
+        <v>818</v>
       </c>
       <c r="O228" t="s" s="2">
-        <v>817</v>
+        <v>819</v>
       </c>
       <c r="P228" s="2"/>
       <c r="Q228" t="s" s="2">
@@ -27830,10 +27844,10 @@
         <v>201</v>
       </c>
       <c r="Z228" t="s" s="2">
-        <v>818</v>
+        <v>820</v>
       </c>
       <c r="AA228" t="s" s="2">
-        <v>819</v>
+        <v>821</v>
       </c>
       <c r="AB228" t="s" s="2">
         <v>75</v>
@@ -27851,7 +27865,7 @@
         <v>75</v>
       </c>
       <c r="AG228" t="s" s="2">
-        <v>814</v>
+        <v>816</v>
       </c>
       <c r="AH228" t="s" s="2">
         <v>76</v>
@@ -27871,10 +27885,10 @@
         <v>386</v>
       </c>
       <c r="B229" t="s" s="2">
-        <v>820</v>
+        <v>822</v>
       </c>
       <c r="C229" t="s" s="2">
-        <v>820</v>
+        <v>822</v>
       </c>
       <c r="D229" s="2"/>
       <c r="E229" t="s" s="2">
@@ -27900,13 +27914,13 @@
         <v>162</v>
       </c>
       <c r="M229" t="s" s="2">
-        <v>821</v>
+        <v>823</v>
       </c>
       <c r="N229" t="s" s="2">
-        <v>822</v>
+        <v>824</v>
       </c>
       <c r="O229" t="s" s="2">
-        <v>823</v>
+        <v>825</v>
       </c>
       <c r="P229" s="2"/>
       <c r="Q229" t="s" s="2">
@@ -27935,10 +27949,10 @@
         <v>173</v>
       </c>
       <c r="Z229" t="s" s="2">
-        <v>824</v>
+        <v>826</v>
       </c>
       <c r="AA229" t="s" s="2">
-        <v>825</v>
+        <v>827</v>
       </c>
       <c r="AB229" t="s" s="2">
         <v>75</v>
@@ -27956,7 +27970,7 @@
         <v>75</v>
       </c>
       <c r="AG229" t="s" s="2">
-        <v>820</v>
+        <v>822</v>
       </c>
       <c r="AH229" t="s" s="2">
         <v>76</v>
@@ -27976,10 +27990,10 @@
         <v>386</v>
       </c>
       <c r="B230" t="s" s="2">
-        <v>826</v>
+        <v>828</v>
       </c>
       <c r="C230" t="s" s="2">
-        <v>826</v>
+        <v>828</v>
       </c>
       <c r="D230" s="2"/>
       <c r="E230" t="s" s="2">
@@ -28005,13 +28019,13 @@
         <v>362</v>
       </c>
       <c r="M230" t="s" s="2">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="N230" t="s" s="2">
-        <v>828</v>
+        <v>830</v>
       </c>
       <c r="O230" t="s" s="2">
-        <v>829</v>
+        <v>831</v>
       </c>
       <c r="P230" s="2"/>
       <c r="Q230" t="s" s="2">
@@ -28061,7 +28075,7 @@
         <v>75</v>
       </c>
       <c r="AG230" t="s" s="2">
-        <v>826</v>
+        <v>828</v>
       </c>
       <c r="AH230" t="s" s="2">
         <v>76</v>
@@ -28081,10 +28095,10 @@
         <v>386</v>
       </c>
       <c r="B231" t="s" s="2">
-        <v>830</v>
+        <v>832</v>
       </c>
       <c r="C231" t="s" s="2">
-        <v>830</v>
+        <v>832</v>
       </c>
       <c r="D231" s="2"/>
       <c r="E231" t="s" s="2">
@@ -28110,10 +28124,10 @@
         <v>237</v>
       </c>
       <c r="M231" t="s" s="2">
-        <v>831</v>
+        <v>833</v>
       </c>
       <c r="N231" t="s" s="2">
-        <v>832</v>
+        <v>834</v>
       </c>
       <c r="O231" s="2"/>
       <c r="P231" s="2"/>
@@ -28121,7 +28135,7 @@
         <v>75</v>
       </c>
       <c r="R231" t="s" s="2">
-        <v>833</v>
+        <v>835</v>
       </c>
       <c r="S231" t="s" s="2">
         <v>75</v>
@@ -28166,7 +28180,7 @@
         <v>75</v>
       </c>
       <c r="AG231" t="s" s="2">
-        <v>830</v>
+        <v>832</v>
       </c>
       <c r="AH231" t="s" s="2">
         <v>76</v>
@@ -28186,10 +28200,10 @@
         <v>386</v>
       </c>
       <c r="B232" t="s" s="2">
-        <v>834</v>
+        <v>836</v>
       </c>
       <c r="C232" t="s" s="2">
-        <v>834</v>
+        <v>836</v>
       </c>
       <c r="D232" s="2"/>
       <c r="E232" t="s" s="2">
@@ -28289,10 +28303,10 @@
         <v>386</v>
       </c>
       <c r="B233" t="s" s="2">
-        <v>835</v>
+        <v>837</v>
       </c>
       <c r="C233" t="s" s="2">
-        <v>835</v>
+        <v>837</v>
       </c>
       <c r="D233" s="2"/>
       <c r="E233" t="s" s="2">
@@ -28394,10 +28408,10 @@
         <v>386</v>
       </c>
       <c r="B234" t="s" s="2">
-        <v>836</v>
+        <v>838</v>
       </c>
       <c r="C234" t="s" s="2">
-        <v>836</v>
+        <v>838</v>
       </c>
       <c r="D234" s="2"/>
       <c r="E234" t="s" s="2">
@@ -28501,10 +28515,10 @@
         <v>386</v>
       </c>
       <c r="B235" t="s" s="2">
-        <v>837</v>
+        <v>839</v>
       </c>
       <c r="C235" t="s" s="2">
-        <v>837</v>
+        <v>839</v>
       </c>
       <c r="D235" s="2"/>
       <c r="E235" t="s" s="2">
@@ -28530,10 +28544,10 @@
         <v>104</v>
       </c>
       <c r="M235" t="s" s="2">
-        <v>838</v>
+        <v>840</v>
       </c>
       <c r="N235" t="s" s="2">
-        <v>839</v>
+        <v>841</v>
       </c>
       <c r="O235" s="2"/>
       <c r="P235" s="2"/>
@@ -28563,10 +28577,10 @@
         <v>152</v>
       </c>
       <c r="Z235" t="s" s="2">
-        <v>840</v>
+        <v>842</v>
       </c>
       <c r="AA235" t="s" s="2">
-        <v>841</v>
+        <v>843</v>
       </c>
       <c r="AB235" t="s" s="2">
         <v>75</v>
@@ -28584,7 +28598,7 @@
         <v>75</v>
       </c>
       <c r="AG235" t="s" s="2">
-        <v>837</v>
+        <v>839</v>
       </c>
       <c r="AH235" t="s" s="2">
         <v>84</v>
@@ -28604,10 +28618,10 @@
         <v>386</v>
       </c>
       <c r="B236" t="s" s="2">
-        <v>842</v>
+        <v>844</v>
       </c>
       <c r="C236" t="s" s="2">
-        <v>842</v>
+        <v>844</v>
       </c>
       <c r="D236" s="2"/>
       <c r="E236" t="s" s="2">
@@ -28633,10 +28647,10 @@
         <v>382</v>
       </c>
       <c r="M236" t="s" s="2">
-        <v>843</v>
+        <v>845</v>
       </c>
       <c r="N236" t="s" s="2">
-        <v>844</v>
+        <v>846</v>
       </c>
       <c r="O236" s="2"/>
       <c r="P236" s="2"/>
@@ -28687,7 +28701,7 @@
         <v>75</v>
       </c>
       <c r="AG236" t="s" s="2">
-        <v>842</v>
+        <v>844</v>
       </c>
       <c r="AH236" t="s" s="2">
         <v>84</v>
@@ -28707,10 +28721,10 @@
         <v>386</v>
       </c>
       <c r="B237" t="s" s="2">
-        <v>845</v>
+        <v>847</v>
       </c>
       <c r="C237" t="s" s="2">
-        <v>845</v>
+        <v>847</v>
       </c>
       <c r="D237" s="2"/>
       <c r="E237" t="s" s="2">
@@ -28736,10 +28750,10 @@
         <v>237</v>
       </c>
       <c r="M237" t="s" s="2">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="N237" t="s" s="2">
-        <v>847</v>
+        <v>849</v>
       </c>
       <c r="O237" s="2"/>
       <c r="P237" s="2"/>
@@ -28790,7 +28804,7 @@
         <v>75</v>
       </c>
       <c r="AG237" t="s" s="2">
-        <v>845</v>
+        <v>847</v>
       </c>
       <c r="AH237" t="s" s="2">
         <v>76</v>
@@ -28810,10 +28824,10 @@
         <v>386</v>
       </c>
       <c r="B238" t="s" s="2">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="C238" t="s" s="2">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="D238" s="2"/>
       <c r="E238" t="s" s="2">
@@ -28913,10 +28927,10 @@
         <v>386</v>
       </c>
       <c r="B239" t="s" s="2">
-        <v>849</v>
+        <v>851</v>
       </c>
       <c r="C239" t="s" s="2">
-        <v>849</v>
+        <v>851</v>
       </c>
       <c r="D239" s="2"/>
       <c r="E239" t="s" s="2">
@@ -29018,10 +29032,10 @@
         <v>386</v>
       </c>
       <c r="B240" t="s" s="2">
-        <v>850</v>
+        <v>852</v>
       </c>
       <c r="C240" t="s" s="2">
-        <v>850</v>
+        <v>852</v>
       </c>
       <c r="D240" s="2"/>
       <c r="E240" t="s" s="2">
@@ -29125,10 +29139,10 @@
         <v>386</v>
       </c>
       <c r="B241" t="s" s="2">
-        <v>851</v>
+        <v>853</v>
       </c>
       <c r="C241" t="s" s="2">
-        <v>851</v>
+        <v>853</v>
       </c>
       <c r="D241" s="2"/>
       <c r="E241" t="s" s="2">
@@ -29154,10 +29168,10 @@
         <v>104</v>
       </c>
       <c r="M241" t="s" s="2">
-        <v>760</v>
+        <v>762</v>
       </c>
       <c r="N241" t="s" s="2">
-        <v>761</v>
+        <v>763</v>
       </c>
       <c r="O241" s="2"/>
       <c r="P241" s="2"/>
@@ -29187,10 +29201,10 @@
         <v>152</v>
       </c>
       <c r="Z241" t="s" s="2">
-        <v>762</v>
+        <v>764</v>
       </c>
       <c r="AA241" t="s" s="2">
-        <v>763</v>
+        <v>765</v>
       </c>
       <c r="AB241" t="s" s="2">
         <v>75</v>
@@ -29208,7 +29222,7 @@
         <v>75</v>
       </c>
       <c r="AG241" t="s" s="2">
-        <v>759</v>
+        <v>761</v>
       </c>
       <c r="AH241" t="s" s="2">
         <v>76</v>
@@ -29228,10 +29242,10 @@
         <v>386</v>
       </c>
       <c r="B242" t="s" s="2">
-        <v>852</v>
+        <v>854</v>
       </c>
       <c r="C242" t="s" s="2">
-        <v>852</v>
+        <v>854</v>
       </c>
       <c r="D242" s="2"/>
       <c r="E242" t="s" s="2">
@@ -29257,10 +29271,10 @@
         <v>362</v>
       </c>
       <c r="M242" t="s" s="2">
-        <v>765</v>
+        <v>767</v>
       </c>
       <c r="N242" t="s" s="2">
-        <v>766</v>
+        <v>768</v>
       </c>
       <c r="O242" s="2"/>
       <c r="P242" s="2"/>
@@ -29311,7 +29325,7 @@
         <v>75</v>
       </c>
       <c r="AG242" t="s" s="2">
-        <v>764</v>
+        <v>766</v>
       </c>
       <c r="AH242" t="s" s="2">
         <v>76</v>
@@ -29331,10 +29345,10 @@
         <v>386</v>
       </c>
       <c r="B243" t="s" s="2">
-        <v>853</v>
+        <v>855</v>
       </c>
       <c r="C243" t="s" s="2">
-        <v>853</v>
+        <v>855</v>
       </c>
       <c r="D243" s="2"/>
       <c r="E243" t="s" s="2">
@@ -29434,10 +29448,10 @@
         <v>386</v>
       </c>
       <c r="B244" t="s" s="2">
-        <v>854</v>
+        <v>856</v>
       </c>
       <c r="C244" t="s" s="2">
-        <v>854</v>
+        <v>856</v>
       </c>
       <c r="D244" s="2"/>
       <c r="E244" t="s" s="2">
@@ -29539,10 +29553,10 @@
         <v>386</v>
       </c>
       <c r="B245" t="s" s="2">
-        <v>855</v>
+        <v>857</v>
       </c>
       <c r="C245" t="s" s="2">
-        <v>855</v>
+        <v>857</v>
       </c>
       <c r="D245" s="2"/>
       <c r="E245" t="s" s="2">
@@ -29568,13 +29582,13 @@
         <v>332</v>
       </c>
       <c r="M245" t="s" s="2">
-        <v>770</v>
+        <v>772</v>
       </c>
       <c r="N245" t="s" s="2">
-        <v>771</v>
+        <v>773</v>
       </c>
       <c r="O245" t="s" s="2">
-        <v>772</v>
+        <v>774</v>
       </c>
       <c r="P245" s="2"/>
       <c r="Q245" t="s" s="2">
@@ -29624,7 +29638,7 @@
         <v>75</v>
       </c>
       <c r="AG245" t="s" s="2">
-        <v>773</v>
+        <v>775</v>
       </c>
       <c r="AH245" t="s" s="2">
         <v>76</v>
@@ -29633,7 +29647,7 @@
         <v>84</v>
       </c>
       <c r="AJ245" t="s" s="2">
-        <v>774</v>
+        <v>776</v>
       </c>
       <c r="AK245" t="s" s="2">
         <v>96</v>
@@ -29644,10 +29658,10 @@
         <v>386</v>
       </c>
       <c r="B246" t="s" s="2">
-        <v>856</v>
+        <v>858</v>
       </c>
       <c r="C246" t="s" s="2">
-        <v>856</v>
+        <v>858</v>
       </c>
       <c r="D246" s="2"/>
       <c r="E246" t="s" s="2">
@@ -29673,20 +29687,20 @@
         <v>332</v>
       </c>
       <c r="M246" t="s" s="2">
-        <v>776</v>
+        <v>778</v>
       </c>
       <c r="N246" t="s" s="2">
-        <v>777</v>
+        <v>779</v>
       </c>
       <c r="O246" t="s" s="2">
-        <v>778</v>
+        <v>780</v>
       </c>
       <c r="P246" s="2"/>
       <c r="Q246" t="s" s="2">
         <v>75</v>
       </c>
       <c r="R246" t="s" s="2">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="S246" t="s" s="2">
         <v>75</v>
@@ -29731,7 +29745,7 @@
         <v>75</v>
       </c>
       <c r="AG246" t="s" s="2">
-        <v>780</v>
+        <v>782</v>
       </c>
       <c r="AH246" t="s" s="2">
         <v>76</v>
@@ -29740,7 +29754,7 @@
         <v>84</v>
       </c>
       <c r="AJ246" t="s" s="2">
-        <v>774</v>
+        <v>776</v>
       </c>
       <c r="AK246" t="s" s="2">
         <v>96</v>
@@ -29751,10 +29765,10 @@
         <v>386</v>
       </c>
       <c r="B247" t="s" s="2">
-        <v>857</v>
+        <v>859</v>
       </c>
       <c r="C247" t="s" s="2">
-        <v>857</v>
+        <v>859</v>
       </c>
       <c r="D247" s="2"/>
       <c r="E247" t="s" s="2">
@@ -29780,10 +29794,10 @@
         <v>237</v>
       </c>
       <c r="M247" t="s" s="2">
-        <v>782</v>
+        <v>784</v>
       </c>
       <c r="N247" t="s" s="2">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="O247" s="2"/>
       <c r="P247" s="2"/>
@@ -29791,7 +29805,7 @@
         <v>75</v>
       </c>
       <c r="R247" t="s" s="2">
-        <v>784</v>
+        <v>786</v>
       </c>
       <c r="S247" t="s" s="2">
         <v>75</v>
@@ -29836,7 +29850,7 @@
         <v>75</v>
       </c>
       <c r="AG247" t="s" s="2">
-        <v>781</v>
+        <v>783</v>
       </c>
       <c r="AH247" t="s" s="2">
         <v>76</v>
@@ -29856,10 +29870,10 @@
         <v>386</v>
       </c>
       <c r="B248" t="s" s="2">
-        <v>858</v>
+        <v>860</v>
       </c>
       <c r="C248" t="s" s="2">
-        <v>858</v>
+        <v>860</v>
       </c>
       <c r="D248" s="2"/>
       <c r="E248" t="s" s="2">
@@ -29959,10 +29973,10 @@
         <v>386</v>
       </c>
       <c r="B249" t="s" s="2">
-        <v>859</v>
+        <v>861</v>
       </c>
       <c r="C249" t="s" s="2">
-        <v>859</v>
+        <v>861</v>
       </c>
       <c r="D249" s="2"/>
       <c r="E249" t="s" s="2">
@@ -30064,10 +30078,10 @@
         <v>386</v>
       </c>
       <c r="B250" t="s" s="2">
-        <v>860</v>
+        <v>862</v>
       </c>
       <c r="C250" t="s" s="2">
-        <v>860</v>
+        <v>862</v>
       </c>
       <c r="D250" s="2"/>
       <c r="E250" t="s" s="2">
@@ -30171,10 +30185,10 @@
         <v>386</v>
       </c>
       <c r="B251" t="s" s="2">
-        <v>861</v>
+        <v>863</v>
       </c>
       <c r="C251" t="s" s="2">
-        <v>861</v>
+        <v>863</v>
       </c>
       <c r="D251" s="2"/>
       <c r="E251" t="s" s="2">
@@ -30200,10 +30214,10 @@
         <v>162</v>
       </c>
       <c r="M251" t="s" s="2">
-        <v>789</v>
+        <v>791</v>
       </c>
       <c r="N251" t="s" s="2">
-        <v>790</v>
+        <v>792</v>
       </c>
       <c r="O251" s="2"/>
       <c r="P251" s="2"/>
@@ -30233,10 +30247,10 @@
         <v>201</v>
       </c>
       <c r="Z251" t="s" s="2">
-        <v>791</v>
+        <v>793</v>
       </c>
       <c r="AA251" t="s" s="2">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="AB251" t="s" s="2">
         <v>75</v>
@@ -30254,7 +30268,7 @@
         <v>75</v>
       </c>
       <c r="AG251" t="s" s="2">
-        <v>788</v>
+        <v>790</v>
       </c>
       <c r="AH251" t="s" s="2">
         <v>84</v>
@@ -30274,10 +30288,10 @@
         <v>386</v>
       </c>
       <c r="B252" t="s" s="2">
-        <v>862</v>
+        <v>864</v>
       </c>
       <c r="C252" t="s" s="2">
-        <v>862</v>
+        <v>864</v>
       </c>
       <c r="D252" s="2"/>
       <c r="E252" t="s" s="2">
@@ -30300,13 +30314,13 @@
         <v>75</v>
       </c>
       <c r="L252" t="s" s="2">
-        <v>794</v>
+        <v>796</v>
       </c>
       <c r="M252" t="s" s="2">
-        <v>795</v>
+        <v>797</v>
       </c>
       <c r="N252" t="s" s="2">
-        <v>796</v>
+        <v>798</v>
       </c>
       <c r="O252" s="2"/>
       <c r="P252" s="2"/>
@@ -30357,7 +30371,7 @@
         <v>75</v>
       </c>
       <c r="AG252" t="s" s="2">
-        <v>793</v>
+        <v>795</v>
       </c>
       <c r="AH252" t="s" s="2">
         <v>84</v>
@@ -30377,10 +30391,10 @@
         <v>386</v>
       </c>
       <c r="B253" t="s" s="2">
-        <v>863</v>
+        <v>865</v>
       </c>
       <c r="C253" t="s" s="2">
-        <v>863</v>
+        <v>865</v>
       </c>
       <c r="D253" s="2"/>
       <c r="E253" t="s" s="2">
@@ -30406,20 +30420,20 @@
         <v>162</v>
       </c>
       <c r="M253" t="s" s="2">
-        <v>798</v>
+        <v>800</v>
       </c>
       <c r="N253" t="s" s="2">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="O253" t="s" s="2">
-        <v>800</v>
+        <v>802</v>
       </c>
       <c r="P253" s="2"/>
       <c r="Q253" t="s" s="2">
         <v>75</v>
       </c>
       <c r="R253" t="s" s="2">
-        <v>801</v>
+        <v>803</v>
       </c>
       <c r="S253" t="s" s="2">
         <v>75</v>
@@ -30443,10 +30457,10 @@
         <v>173</v>
       </c>
       <c r="Z253" t="s" s="2">
-        <v>802</v>
+        <v>804</v>
       </c>
       <c r="AA253" t="s" s="2">
-        <v>803</v>
+        <v>805</v>
       </c>
       <c r="AB253" t="s" s="2">
         <v>75</v>
@@ -30464,7 +30478,7 @@
         <v>75</v>
       </c>
       <c r="AG253" t="s" s="2">
-        <v>797</v>
+        <v>799</v>
       </c>
       <c r="AH253" t="s" s="2">
         <v>76</v>
@@ -30484,10 +30498,10 @@
         <v>386</v>
       </c>
       <c r="B254" t="s" s="2">
-        <v>864</v>
+        <v>866</v>
       </c>
       <c r="C254" t="s" s="2">
-        <v>864</v>
+        <v>866</v>
       </c>
       <c r="D254" s="2"/>
       <c r="E254" t="s" s="2">
@@ -30513,13 +30527,13 @@
         <v>338</v>
       </c>
       <c r="M254" t="s" s="2">
-        <v>805</v>
+        <v>807</v>
       </c>
       <c r="N254" t="s" s="2">
-        <v>806</v>
+        <v>808</v>
       </c>
       <c r="O254" t="s" s="2">
-        <v>807</v>
+        <v>809</v>
       </c>
       <c r="P254" s="2"/>
       <c r="Q254" t="s" s="2">
@@ -30569,7 +30583,7 @@
         <v>75</v>
       </c>
       <c r="AG254" t="s" s="2">
-        <v>804</v>
+        <v>806</v>
       </c>
       <c r="AH254" t="s" s="2">
         <v>76</v>
@@ -30589,10 +30603,10 @@
         <v>386</v>
       </c>
       <c r="B255" t="s" s="2">
-        <v>865</v>
+        <v>867</v>
       </c>
       <c r="C255" t="s" s="2">
-        <v>865</v>
+        <v>867</v>
       </c>
       <c r="D255" s="2"/>
       <c r="E255" t="s" s="2">
@@ -30618,13 +30632,13 @@
         <v>338</v>
       </c>
       <c r="M255" t="s" s="2">
-        <v>809</v>
+        <v>811</v>
       </c>
       <c r="N255" t="s" s="2">
-        <v>810</v>
+        <v>812</v>
       </c>
       <c r="O255" t="s" s="2">
-        <v>811</v>
+        <v>813</v>
       </c>
       <c r="P255" s="2"/>
       <c r="Q255" t="s" s="2">
@@ -30653,10 +30667,10 @@
         <v>201</v>
       </c>
       <c r="Z255" t="s" s="2">
-        <v>812</v>
+        <v>814</v>
       </c>
       <c r="AA255" t="s" s="2">
-        <v>813</v>
+        <v>815</v>
       </c>
       <c r="AB255" t="s" s="2">
         <v>75</v>
@@ -30674,7 +30688,7 @@
         <v>75</v>
       </c>
       <c r="AG255" t="s" s="2">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="AH255" t="s" s="2">
         <v>76</v>
@@ -30694,10 +30708,10 @@
         <v>386</v>
       </c>
       <c r="B256" t="s" s="2">
-        <v>866</v>
+        <v>868</v>
       </c>
       <c r="C256" t="s" s="2">
-        <v>866</v>
+        <v>868</v>
       </c>
       <c r="D256" s="2"/>
       <c r="E256" t="s" s="2">
@@ -30723,13 +30737,13 @@
         <v>338</v>
       </c>
       <c r="M256" t="s" s="2">
-        <v>815</v>
+        <v>817</v>
       </c>
       <c r="N256" t="s" s="2">
-        <v>816</v>
+        <v>818</v>
       </c>
       <c r="O256" t="s" s="2">
-        <v>817</v>
+        <v>819</v>
       </c>
       <c r="P256" s="2"/>
       <c r="Q256" t="s" s="2">
@@ -30758,10 +30772,10 @@
         <v>201</v>
       </c>
       <c r="Z256" t="s" s="2">
-        <v>818</v>
+        <v>820</v>
       </c>
       <c r="AA256" t="s" s="2">
-        <v>819</v>
+        <v>821</v>
       </c>
       <c r="AB256" t="s" s="2">
         <v>75</v>
@@ -30779,7 +30793,7 @@
         <v>75</v>
       </c>
       <c r="AG256" t="s" s="2">
-        <v>814</v>
+        <v>816</v>
       </c>
       <c r="AH256" t="s" s="2">
         <v>76</v>
@@ -30799,10 +30813,10 @@
         <v>386</v>
       </c>
       <c r="B257" t="s" s="2">
-        <v>867</v>
+        <v>869</v>
       </c>
       <c r="C257" t="s" s="2">
-        <v>867</v>
+        <v>869</v>
       </c>
       <c r="D257" s="2"/>
       <c r="E257" t="s" s="2">
@@ -30828,13 +30842,13 @@
         <v>162</v>
       </c>
       <c r="M257" t="s" s="2">
-        <v>821</v>
+        <v>823</v>
       </c>
       <c r="N257" t="s" s="2">
-        <v>822</v>
+        <v>824</v>
       </c>
       <c r="O257" t="s" s="2">
-        <v>823</v>
+        <v>825</v>
       </c>
       <c r="P257" s="2"/>
       <c r="Q257" t="s" s="2">
@@ -30864,7 +30878,7 @@
       </c>
       <c r="Z257" s="2"/>
       <c r="AA257" t="s" s="2">
-        <v>868</v>
+        <v>870</v>
       </c>
       <c r="AB257" t="s" s="2">
         <v>75</v>
@@ -30882,7 +30896,7 @@
         <v>75</v>
       </c>
       <c r="AG257" t="s" s="2">
-        <v>820</v>
+        <v>822</v>
       </c>
       <c r="AH257" t="s" s="2">
         <v>76</v>
@@ -30902,10 +30916,10 @@
         <v>386</v>
       </c>
       <c r="B258" t="s" s="2">
-        <v>869</v>
+        <v>871</v>
       </c>
       <c r="C258" t="s" s="2">
-        <v>869</v>
+        <v>871</v>
       </c>
       <c r="D258" s="2"/>
       <c r="E258" t="s" s="2">
@@ -31005,10 +31019,10 @@
         <v>386</v>
       </c>
       <c r="B259" t="s" s="2">
-        <v>870</v>
+        <v>872</v>
       </c>
       <c r="C259" t="s" s="2">
-        <v>870</v>
+        <v>872</v>
       </c>
       <c r="D259" s="2"/>
       <c r="E259" t="s" s="2">
@@ -31110,10 +31124,10 @@
         <v>386</v>
       </c>
       <c r="B260" t="s" s="2">
-        <v>871</v>
+        <v>873</v>
       </c>
       <c r="C260" t="s" s="2">
-        <v>871</v>
+        <v>873</v>
       </c>
       <c r="D260" s="2"/>
       <c r="E260" t="s" s="2">
@@ -31217,10 +31231,10 @@
         <v>386</v>
       </c>
       <c r="B261" t="s" s="2">
-        <v>872</v>
+        <v>874</v>
       </c>
       <c r="C261" t="s" s="2">
-        <v>872</v>
+        <v>874</v>
       </c>
       <c r="D261" s="2"/>
       <c r="E261" t="s" s="2">
@@ -31320,10 +31334,10 @@
         <v>386</v>
       </c>
       <c r="B262" t="s" s="2">
-        <v>873</v>
+        <v>875</v>
       </c>
       <c r="C262" t="s" s="2">
-        <v>873</v>
+        <v>875</v>
       </c>
       <c r="D262" s="2"/>
       <c r="E262" t="s" s="2">
@@ -31425,10 +31439,10 @@
         <v>386</v>
       </c>
       <c r="B263" t="s" s="2">
-        <v>874</v>
+        <v>876</v>
       </c>
       <c r="C263" t="s" s="2">
-        <v>874</v>
+        <v>876</v>
       </c>
       <c r="D263" s="2"/>
       <c r="E263" t="s" s="2">
@@ -31532,10 +31546,10 @@
         <v>386</v>
       </c>
       <c r="B264" t="s" s="2">
-        <v>875</v>
+        <v>877</v>
       </c>
       <c r="C264" t="s" s="2">
-        <v>875</v>
+        <v>877</v>
       </c>
       <c r="D264" s="2"/>
       <c r="E264" t="s" s="2">
@@ -31637,10 +31651,10 @@
         <v>386</v>
       </c>
       <c r="B265" t="s" s="2">
-        <v>876</v>
+        <v>878</v>
       </c>
       <c r="C265" t="s" s="2">
-        <v>876</v>
+        <v>878</v>
       </c>
       <c r="D265" s="2"/>
       <c r="E265" t="s" s="2">
@@ -31742,10 +31756,10 @@
         <v>386</v>
       </c>
       <c r="B266" t="s" s="2">
-        <v>877</v>
+        <v>879</v>
       </c>
       <c r="C266" t="s" s="2">
-        <v>877</v>
+        <v>879</v>
       </c>
       <c r="D266" s="2"/>
       <c r="E266" t="s" s="2">
@@ -31847,10 +31861,10 @@
         <v>386</v>
       </c>
       <c r="B267" t="s" s="2">
-        <v>878</v>
+        <v>880</v>
       </c>
       <c r="C267" t="s" s="2">
-        <v>878</v>
+        <v>880</v>
       </c>
       <c r="D267" s="2"/>
       <c r="E267" t="s" s="2">
@@ -31954,10 +31968,10 @@
         <v>386</v>
       </c>
       <c r="B268" t="s" s="2">
-        <v>879</v>
+        <v>881</v>
       </c>
       <c r="C268" t="s" s="2">
-        <v>879</v>
+        <v>881</v>
       </c>
       <c r="D268" s="2"/>
       <c r="E268" t="s" s="2">
@@ -32061,10 +32075,10 @@
         <v>386</v>
       </c>
       <c r="B269" t="s" s="2">
-        <v>880</v>
+        <v>882</v>
       </c>
       <c r="C269" t="s" s="2">
-        <v>880</v>
+        <v>882</v>
       </c>
       <c r="D269" s="2"/>
       <c r="E269" t="s" s="2">
@@ -32090,13 +32104,13 @@
         <v>362</v>
       </c>
       <c r="M269" t="s" s="2">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="N269" t="s" s="2">
-        <v>828</v>
+        <v>830</v>
       </c>
       <c r="O269" t="s" s="2">
-        <v>829</v>
+        <v>831</v>
       </c>
       <c r="P269" s="2"/>
       <c r="Q269" t="s" s="2">
@@ -32146,7 +32160,7 @@
         <v>75</v>
       </c>
       <c r="AG269" t="s" s="2">
-        <v>826</v>
+        <v>828</v>
       </c>
       <c r="AH269" t="s" s="2">
         <v>76</v>
@@ -32166,10 +32180,10 @@
         <v>386</v>
       </c>
       <c r="B270" t="s" s="2">
-        <v>881</v>
+        <v>883</v>
       </c>
       <c r="C270" t="s" s="2">
-        <v>881</v>
+        <v>883</v>
       </c>
       <c r="D270" s="2"/>
       <c r="E270" t="s" s="2">
@@ -32195,10 +32209,10 @@
         <v>237</v>
       </c>
       <c r="M270" t="s" s="2">
-        <v>831</v>
+        <v>833</v>
       </c>
       <c r="N270" t="s" s="2">
-        <v>832</v>
+        <v>834</v>
       </c>
       <c r="O270" s="2"/>
       <c r="P270" s="2"/>
@@ -32206,7 +32220,7 @@
         <v>75</v>
       </c>
       <c r="R270" t="s" s="2">
-        <v>833</v>
+        <v>835</v>
       </c>
       <c r="S270" t="s" s="2">
         <v>75</v>
@@ -32251,7 +32265,7 @@
         <v>75</v>
       </c>
       <c r="AG270" t="s" s="2">
-        <v>830</v>
+        <v>832</v>
       </c>
       <c r="AH270" t="s" s="2">
         <v>76</v>
@@ -32271,10 +32285,10 @@
         <v>386</v>
       </c>
       <c r="B271" t="s" s="2">
-        <v>882</v>
+        <v>884</v>
       </c>
       <c r="C271" t="s" s="2">
-        <v>882</v>
+        <v>884</v>
       </c>
       <c r="D271" s="2"/>
       <c r="E271" t="s" s="2">
@@ -32374,10 +32388,10 @@
         <v>386</v>
       </c>
       <c r="B272" t="s" s="2">
-        <v>883</v>
+        <v>885</v>
       </c>
       <c r="C272" t="s" s="2">
-        <v>883</v>
+        <v>885</v>
       </c>
       <c r="D272" s="2"/>
       <c r="E272" t="s" s="2">
@@ -32479,10 +32493,10 @@
         <v>386</v>
       </c>
       <c r="B273" t="s" s="2">
-        <v>884</v>
+        <v>886</v>
       </c>
       <c r="C273" t="s" s="2">
-        <v>884</v>
+        <v>886</v>
       </c>
       <c r="D273" s="2"/>
       <c r="E273" t="s" s="2">
@@ -32586,10 +32600,10 @@
         <v>386</v>
       </c>
       <c r="B274" t="s" s="2">
-        <v>885</v>
+        <v>887</v>
       </c>
       <c r="C274" t="s" s="2">
-        <v>885</v>
+        <v>887</v>
       </c>
       <c r="D274" s="2"/>
       <c r="E274" t="s" s="2">
@@ -32615,10 +32629,10 @@
         <v>104</v>
       </c>
       <c r="M274" t="s" s="2">
-        <v>838</v>
+        <v>840</v>
       </c>
       <c r="N274" t="s" s="2">
-        <v>839</v>
+        <v>841</v>
       </c>
       <c r="O274" s="2"/>
       <c r="P274" s="2"/>
@@ -32648,10 +32662,10 @@
         <v>152</v>
       </c>
       <c r="Z274" t="s" s="2">
-        <v>840</v>
+        <v>842</v>
       </c>
       <c r="AA274" t="s" s="2">
-        <v>841</v>
+        <v>843</v>
       </c>
       <c r="AB274" t="s" s="2">
         <v>75</v>
@@ -32669,7 +32683,7 @@
         <v>75</v>
       </c>
       <c r="AG274" t="s" s="2">
-        <v>837</v>
+        <v>839</v>
       </c>
       <c r="AH274" t="s" s="2">
         <v>84</v>
@@ -32689,10 +32703,10 @@
         <v>386</v>
       </c>
       <c r="B275" t="s" s="2">
-        <v>886</v>
+        <v>888</v>
       </c>
       <c r="C275" t="s" s="2">
-        <v>886</v>
+        <v>888</v>
       </c>
       <c r="D275" s="2"/>
       <c r="E275" t="s" s="2">
@@ -32718,10 +32732,10 @@
         <v>382</v>
       </c>
       <c r="M275" t="s" s="2">
-        <v>843</v>
+        <v>845</v>
       </c>
       <c r="N275" t="s" s="2">
-        <v>844</v>
+        <v>846</v>
       </c>
       <c r="O275" s="2"/>
       <c r="P275" s="2"/>
@@ -32772,7 +32786,7 @@
         <v>75</v>
       </c>
       <c r="AG275" t="s" s="2">
-        <v>842</v>
+        <v>844</v>
       </c>
       <c r="AH275" t="s" s="2">
         <v>84</v>
@@ -32792,10 +32806,10 @@
         <v>386</v>
       </c>
       <c r="B276" t="s" s="2">
-        <v>887</v>
+        <v>889</v>
       </c>
       <c r="C276" t="s" s="2">
-        <v>887</v>
+        <v>889</v>
       </c>
       <c r="D276" s="2"/>
       <c r="E276" t="s" s="2">
@@ -32821,10 +32835,10 @@
         <v>75</v>
       </c>
       <c r="M276" t="s" s="2">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="N276" t="s" s="2">
-        <v>847</v>
+        <v>849</v>
       </c>
       <c r="O276" s="2"/>
       <c r="P276" s="2"/>
@@ -32875,7 +32889,7 @@
         <v>75</v>
       </c>
       <c r="AG276" t="s" s="2">
-        <v>845</v>
+        <v>847</v>
       </c>
       <c r="AH276" t="s" s="2">
         <v>76</v>
@@ -32892,17 +32906,17 @@
     </row>
     <row r="277">
       <c r="A277" t="s" s="2">
-        <v>888</v>
+        <v>890</v>
       </c>
       <c r="B277" t="s" s="2">
-        <v>893</v>
+        <v>895</v>
       </c>
       <c r="C277" t="s" s="2">
-        <v>893</v>
+        <v>895</v>
       </c>
       <c r="D277" s="2"/>
       <c r="E277" t="s" s="2">
-        <v>895</v>
+        <v>897</v>
       </c>
       <c r="F277" s="2"/>
       <c r="G277" t="s" s="2">
@@ -32924,13 +32938,13 @@
         <v>78</v>
       </c>
       <c r="M277" t="s" s="2">
-        <v>896</v>
+        <v>898</v>
       </c>
       <c r="N277" t="s" s="2">
-        <v>897</v>
+        <v>899</v>
       </c>
       <c r="O277" t="s" s="2">
-        <v>898</v>
+        <v>900</v>
       </c>
       <c r="P277" s="2"/>
       <c r="Q277" t="s" s="2">
@@ -32980,7 +32994,7 @@
         <v>75</v>
       </c>
       <c r="AG277" t="s" s="2">
-        <v>893</v>
+        <v>895</v>
       </c>
       <c r="AH277" t="s" s="2">
         <v>76</v>
@@ -32997,13 +33011,13 @@
     </row>
     <row r="278">
       <c r="A278" t="s" s="2">
-        <v>888</v>
+        <v>890</v>
       </c>
       <c r="B278" t="s" s="2">
-        <v>899</v>
+        <v>901</v>
       </c>
       <c r="C278" t="s" s="2">
-        <v>899</v>
+        <v>901</v>
       </c>
       <c r="D278" s="2"/>
       <c r="E278" t="s" s="2">
@@ -33102,13 +33116,13 @@
     </row>
     <row r="279">
       <c r="A279" t="s" s="2">
-        <v>888</v>
+        <v>890</v>
       </c>
       <c r="B279" t="s" s="2">
-        <v>900</v>
+        <v>902</v>
       </c>
       <c r="C279" t="s" s="2">
-        <v>900</v>
+        <v>902</v>
       </c>
       <c r="D279" s="2"/>
       <c r="E279" t="s" s="2">
@@ -33205,13 +33219,13 @@
     </row>
     <row r="280">
       <c r="A280" t="s" s="2">
-        <v>888</v>
+        <v>890</v>
       </c>
       <c r="B280" t="s" s="2">
-        <v>901</v>
+        <v>903</v>
       </c>
       <c r="C280" t="s" s="2">
-        <v>901</v>
+        <v>903</v>
       </c>
       <c r="D280" s="2"/>
       <c r="E280" t="s" s="2">
@@ -33310,13 +33324,13 @@
     </row>
     <row r="281">
       <c r="A281" t="s" s="2">
-        <v>888</v>
+        <v>890</v>
       </c>
       <c r="B281" t="s" s="2">
-        <v>902</v>
+        <v>904</v>
       </c>
       <c r="C281" t="s" s="2">
-        <v>902</v>
+        <v>904</v>
       </c>
       <c r="D281" s="2"/>
       <c r="E281" t="s" s="2">
@@ -33415,13 +33429,13 @@
     </row>
     <row r="282">
       <c r="A282" t="s" s="2">
-        <v>888</v>
+        <v>890</v>
       </c>
       <c r="B282" t="s" s="2">
-        <v>903</v>
+        <v>905</v>
       </c>
       <c r="C282" t="s" s="2">
-        <v>903</v>
+        <v>905</v>
       </c>
       <c r="D282" s="2"/>
       <c r="E282" t="s" s="2">
@@ -33520,13 +33534,13 @@
     </row>
     <row r="283">
       <c r="A283" t="s" s="2">
-        <v>888</v>
+        <v>890</v>
       </c>
       <c r="B283" t="s" s="2">
-        <v>904</v>
+        <v>906</v>
       </c>
       <c r="C283" t="s" s="2">
-        <v>904</v>
+        <v>906</v>
       </c>
       <c r="D283" s="2"/>
       <c r="E283" t="s" s="2">
@@ -33625,13 +33639,13 @@
     </row>
     <row r="284">
       <c r="A284" t="s" s="2">
-        <v>888</v>
+        <v>890</v>
       </c>
       <c r="B284" t="s" s="2">
-        <v>905</v>
+        <v>907</v>
       </c>
       <c r="C284" t="s" s="2">
-        <v>905</v>
+        <v>907</v>
       </c>
       <c r="D284" s="2"/>
       <c r="E284" t="s" s="2">
@@ -33730,13 +33744,13 @@
     </row>
     <row r="285">
       <c r="A285" t="s" s="2">
-        <v>888</v>
+        <v>890</v>
       </c>
       <c r="B285" t="s" s="2">
-        <v>906</v>
+        <v>908</v>
       </c>
       <c r="C285" t="s" s="2">
-        <v>906</v>
+        <v>908</v>
       </c>
       <c r="D285" s="2"/>
       <c r="E285" t="s" s="2">
@@ -33837,13 +33851,13 @@
     </row>
     <row r="286">
       <c r="A286" t="s" s="2">
-        <v>888</v>
+        <v>890</v>
       </c>
       <c r="B286" t="s" s="2">
-        <v>907</v>
+        <v>909</v>
       </c>
       <c r="C286" t="s" s="2">
-        <v>907</v>
+        <v>909</v>
       </c>
       <c r="D286" s="2"/>
       <c r="E286" t="s" s="2">
@@ -33866,16 +33880,16 @@
         <v>85</v>
       </c>
       <c r="L286" t="s" s="2">
-        <v>908</v>
+        <v>910</v>
       </c>
       <c r="M286" t="s" s="2">
-        <v>909</v>
+        <v>911</v>
       </c>
       <c r="N286" t="s" s="2">
-        <v>910</v>
+        <v>912</v>
       </c>
       <c r="O286" t="s" s="2">
-        <v>911</v>
+        <v>913</v>
       </c>
       <c r="P286" s="2"/>
       <c r="Q286" t="s" s="2">
@@ -33925,7 +33939,7 @@
         <v>75</v>
       </c>
       <c r="AG286" t="s" s="2">
-        <v>907</v>
+        <v>909</v>
       </c>
       <c r="AH286" t="s" s="2">
         <v>84</v>
@@ -33942,13 +33956,13 @@
     </row>
     <row r="287">
       <c r="A287" t="s" s="2">
-        <v>888</v>
+        <v>890</v>
       </c>
       <c r="B287" t="s" s="2">
-        <v>912</v>
+        <v>914</v>
       </c>
       <c r="C287" t="s" s="2">
-        <v>912</v>
+        <v>914</v>
       </c>
       <c r="D287" s="2"/>
       <c r="E287" t="s" s="2">
@@ -34045,13 +34059,13 @@
     </row>
     <row r="288">
       <c r="A288" t="s" s="2">
-        <v>888</v>
+        <v>890</v>
       </c>
       <c r="B288" t="s" s="2">
-        <v>913</v>
+        <v>915</v>
       </c>
       <c r="C288" t="s" s="2">
-        <v>913</v>
+        <v>915</v>
       </c>
       <c r="D288" s="2"/>
       <c r="E288" t="s" s="2">
@@ -34150,13 +34164,13 @@
     </row>
     <row r="289">
       <c r="A289" t="s" s="2">
-        <v>888</v>
+        <v>890</v>
       </c>
       <c r="B289" t="s" s="2">
-        <v>914</v>
+        <v>916</v>
       </c>
       <c r="C289" t="s" s="2">
-        <v>914</v>
+        <v>916</v>
       </c>
       <c r="D289" s="2"/>
       <c r="E289" t="s" s="2">
@@ -34255,13 +34269,13 @@
     </row>
     <row r="290">
       <c r="A290" t="s" s="2">
-        <v>888</v>
+        <v>890</v>
       </c>
       <c r="B290" t="s" s="2">
-        <v>915</v>
+        <v>917</v>
       </c>
       <c r="C290" t="s" s="2">
-        <v>915</v>
+        <v>917</v>
       </c>
       <c r="D290" s="2"/>
       <c r="E290" t="s" s="2">
@@ -34360,13 +34374,13 @@
     </row>
     <row r="291">
       <c r="A291" t="s" s="2">
-        <v>888</v>
+        <v>890</v>
       </c>
       <c r="B291" t="s" s="2">
-        <v>916</v>
+        <v>918</v>
       </c>
       <c r="C291" t="s" s="2">
-        <v>916</v>
+        <v>918</v>
       </c>
       <c r="D291" s="2"/>
       <c r="E291" t="s" s="2">
@@ -34465,13 +34479,13 @@
     </row>
     <row r="292">
       <c r="A292" t="s" s="2">
-        <v>888</v>
+        <v>890</v>
       </c>
       <c r="B292" t="s" s="2">
-        <v>917</v>
+        <v>919</v>
       </c>
       <c r="C292" t="s" s="2">
-        <v>917</v>
+        <v>919</v>
       </c>
       <c r="D292" s="2"/>
       <c r="E292" t="s" s="2">
@@ -34570,13 +34584,13 @@
     </row>
     <row r="293">
       <c r="A293" t="s" s="2">
-        <v>888</v>
+        <v>890</v>
       </c>
       <c r="B293" t="s" s="2">
-        <v>918</v>
+        <v>920</v>
       </c>
       <c r="C293" t="s" s="2">
-        <v>918</v>
+        <v>920</v>
       </c>
       <c r="D293" s="2"/>
       <c r="E293" t="s" s="2">
@@ -34599,16 +34613,16 @@
         <v>75</v>
       </c>
       <c r="L293" t="s" s="2">
-        <v>919</v>
+        <v>921</v>
       </c>
       <c r="M293" t="s" s="2">
-        <v>920</v>
+        <v>922</v>
       </c>
       <c r="N293" t="s" s="2">
-        <v>921</v>
+        <v>923</v>
       </c>
       <c r="O293" t="s" s="2">
-        <v>922</v>
+        <v>924</v>
       </c>
       <c r="P293" s="2"/>
       <c r="Q293" t="s" s="2">
@@ -34658,7 +34672,7 @@
         <v>75</v>
       </c>
       <c r="AG293" t="s" s="2">
-        <v>918</v>
+        <v>920</v>
       </c>
       <c r="AH293" t="s" s="2">
         <v>76</v>
@@ -34675,13 +34689,13 @@
     </row>
     <row r="294">
       <c r="A294" t="s" s="2">
-        <v>888</v>
+        <v>890</v>
       </c>
       <c r="B294" t="s" s="2">
-        <v>923</v>
+        <v>925</v>
       </c>
       <c r="C294" t="s" s="2">
-        <v>923</v>
+        <v>925</v>
       </c>
       <c r="D294" s="2"/>
       <c r="E294" t="s" s="2">
@@ -34707,13 +34721,13 @@
         <v>217</v>
       </c>
       <c r="M294" t="s" s="2">
-        <v>924</v>
+        <v>926</v>
       </c>
       <c r="N294" t="s" s="2">
-        <v>925</v>
+        <v>927</v>
       </c>
       <c r="O294" t="s" s="2">
-        <v>926</v>
+        <v>928</v>
       </c>
       <c r="P294" s="2"/>
       <c r="Q294" t="s" s="2">
@@ -34763,7 +34777,7 @@
         <v>75</v>
       </c>
       <c r="AG294" t="s" s="2">
-        <v>923</v>
+        <v>925</v>
       </c>
       <c r="AH294" t="s" s="2">
         <v>84</v>
@@ -34780,13 +34794,13 @@
     </row>
     <row r="295">
       <c r="A295" t="s" s="2">
-        <v>888</v>
+        <v>890</v>
       </c>
       <c r="B295" t="s" s="2">
-        <v>927</v>
+        <v>929</v>
       </c>
       <c r="C295" t="s" s="2">
-        <v>927</v>
+        <v>929</v>
       </c>
       <c r="D295" s="2"/>
       <c r="E295" t="s" s="2">
@@ -34812,13 +34826,13 @@
         <v>98</v>
       </c>
       <c r="M295" t="s" s="2">
-        <v>928</v>
+        <v>930</v>
       </c>
       <c r="N295" t="s" s="2">
-        <v>929</v>
+        <v>931</v>
       </c>
       <c r="O295" t="s" s="2">
-        <v>930</v>
+        <v>932</v>
       </c>
       <c r="P295" s="2"/>
       <c r="Q295" t="s" s="2">
@@ -34868,7 +34882,7 @@
         <v>75</v>
       </c>
       <c r="AG295" t="s" s="2">
-        <v>927</v>
+        <v>929</v>
       </c>
       <c r="AH295" t="s" s="2">
         <v>76</v>
@@ -34885,13 +34899,13 @@
     </row>
     <row r="296">
       <c r="A296" t="s" s="2">
-        <v>888</v>
+        <v>890</v>
       </c>
       <c r="B296" t="s" s="2">
-        <v>931</v>
+        <v>933</v>
       </c>
       <c r="C296" t="s" s="2">
-        <v>931</v>
+        <v>933</v>
       </c>
       <c r="D296" s="2"/>
       <c r="E296" t="s" s="2">
@@ -34914,13 +34928,13 @@
         <v>75</v>
       </c>
       <c r="L296" t="s" s="2">
-        <v>932</v>
+        <v>934</v>
       </c>
       <c r="M296" t="s" s="2">
-        <v>933</v>
+        <v>935</v>
       </c>
       <c r="N296" t="s" s="2">
-        <v>934</v>
+        <v>936</v>
       </c>
       <c r="O296" s="2"/>
       <c r="P296" s="2"/>
@@ -34971,7 +34985,7 @@
         <v>75</v>
       </c>
       <c r="AG296" t="s" s="2">
-        <v>931</v>
+        <v>933</v>
       </c>
       <c r="AH296" t="s" s="2">
         <v>76</v>
@@ -34988,13 +35002,13 @@
     </row>
     <row r="297">
       <c r="A297" t="s" s="2">
-        <v>888</v>
+        <v>890</v>
       </c>
       <c r="B297" t="s" s="2">
-        <v>935</v>
+        <v>937</v>
       </c>
       <c r="C297" t="s" s="2">
-        <v>935</v>
+        <v>937</v>
       </c>
       <c r="D297" s="2"/>
       <c r="E297" t="s" s="2">
@@ -35020,10 +35034,10 @@
         <v>162</v>
       </c>
       <c r="M297" t="s" s="2">
-        <v>936</v>
+        <v>938</v>
       </c>
       <c r="N297" t="s" s="2">
-        <v>937</v>
+        <v>939</v>
       </c>
       <c r="O297" s="2"/>
       <c r="P297" s="2"/>
@@ -35053,10 +35067,10 @@
         <v>201</v>
       </c>
       <c r="Z297" t="s" s="2">
-        <v>938</v>
+        <v>940</v>
       </c>
       <c r="AA297" t="s" s="2">
-        <v>813</v>
+        <v>815</v>
       </c>
       <c r="AB297" t="s" s="2">
         <v>75</v>
@@ -35074,7 +35088,7 @@
         <v>75</v>
       </c>
       <c r="AG297" t="s" s="2">
-        <v>935</v>
+        <v>937</v>
       </c>
       <c r="AH297" t="s" s="2">
         <v>76</v>
@@ -35091,13 +35105,13 @@
     </row>
     <row r="298">
       <c r="A298" t="s" s="2">
-        <v>888</v>
+        <v>890</v>
       </c>
       <c r="B298" t="s" s="2">
-        <v>939</v>
+        <v>941</v>
       </c>
       <c r="C298" t="s" s="2">
-        <v>939</v>
+        <v>941</v>
       </c>
       <c r="D298" s="2"/>
       <c r="E298" t="s" s="2">
@@ -35123,10 +35137,10 @@
         <v>162</v>
       </c>
       <c r="M298" t="s" s="2">
-        <v>940</v>
+        <v>942</v>
       </c>
       <c r="N298" t="s" s="2">
-        <v>941</v>
+        <v>943</v>
       </c>
       <c r="O298" s="2"/>
       <c r="P298" s="2"/>
@@ -35156,10 +35170,10 @@
         <v>201</v>
       </c>
       <c r="Z298" t="s" s="2">
-        <v>942</v>
+        <v>944</v>
       </c>
       <c r="AA298" t="s" s="2">
-        <v>943</v>
+        <v>945</v>
       </c>
       <c r="AB298" t="s" s="2">
         <v>75</v>
@@ -35177,7 +35191,7 @@
         <v>75</v>
       </c>
       <c r="AG298" t="s" s="2">
-        <v>939</v>
+        <v>941</v>
       </c>
       <c r="AH298" t="s" s="2">
         <v>76</v>
@@ -35194,13 +35208,13 @@
     </row>
     <row r="299">
       <c r="A299" t="s" s="2">
-        <v>888</v>
+        <v>890</v>
       </c>
       <c r="B299" t="s" s="2">
-        <v>944</v>
+        <v>946</v>
       </c>
       <c r="C299" t="s" s="2">
-        <v>944</v>
+        <v>946</v>
       </c>
       <c r="D299" s="2"/>
       <c r="E299" t="s" s="2">
@@ -35226,16 +35240,16 @@
         <v>237</v>
       </c>
       <c r="M299" t="s" s="2">
-        <v>945</v>
+        <v>947</v>
       </c>
       <c r="N299" t="s" s="2">
-        <v>946</v>
+        <v>948</v>
       </c>
       <c r="O299" t="s" s="2">
-        <v>947</v>
+        <v>949</v>
       </c>
       <c r="P299" t="s" s="2">
-        <v>948</v>
+        <v>950</v>
       </c>
       <c r="Q299" t="s" s="2">
         <v>75</v>
@@ -35284,7 +35298,7 @@
         <v>75</v>
       </c>
       <c r="AG299" t="s" s="2">
-        <v>944</v>
+        <v>946</v>
       </c>
       <c r="AH299" t="s" s="2">
         <v>84</v>
@@ -35301,13 +35315,13 @@
     </row>
     <row r="300">
       <c r="A300" t="s" s="2">
-        <v>888</v>
+        <v>890</v>
       </c>
       <c r="B300" t="s" s="2">
-        <v>949</v>
+        <v>951</v>
       </c>
       <c r="C300" t="s" s="2">
-        <v>949</v>
+        <v>951</v>
       </c>
       <c r="D300" s="2"/>
       <c r="E300" t="s" s="2">
@@ -35404,13 +35418,13 @@
     </row>
     <row r="301">
       <c r="A301" t="s" s="2">
-        <v>888</v>
+        <v>890</v>
       </c>
       <c r="B301" t="s" s="2">
-        <v>950</v>
+        <v>952</v>
       </c>
       <c r="C301" t="s" s="2">
-        <v>950</v>
+        <v>952</v>
       </c>
       <c r="D301" s="2"/>
       <c r="E301" t="s" s="2">
@@ -35509,13 +35523,13 @@
     </row>
     <row r="302">
       <c r="A302" t="s" s="2">
-        <v>888</v>
+        <v>890</v>
       </c>
       <c r="B302" t="s" s="2">
-        <v>951</v>
+        <v>953</v>
       </c>
       <c r="C302" t="s" s="2">
-        <v>951</v>
+        <v>953</v>
       </c>
       <c r="D302" s="2"/>
       <c r="E302" t="s" s="2">
@@ -35616,13 +35630,13 @@
     </row>
     <row r="303">
       <c r="A303" t="s" s="2">
-        <v>888</v>
+        <v>890</v>
       </c>
       <c r="B303" t="s" s="2">
-        <v>952</v>
+        <v>954</v>
       </c>
       <c r="C303" t="s" s="2">
-        <v>952</v>
+        <v>954</v>
       </c>
       <c r="D303" s="2"/>
       <c r="E303" t="s" s="2">
@@ -35648,13 +35662,13 @@
         <v>162</v>
       </c>
       <c r="M303" t="s" s="2">
-        <v>953</v>
+        <v>955</v>
       </c>
       <c r="N303" t="s" s="2">
-        <v>954</v>
+        <v>956</v>
       </c>
       <c r="O303" t="s" s="2">
-        <v>955</v>
+        <v>957</v>
       </c>
       <c r="P303" s="2"/>
       <c r="Q303" t="s" s="2">
@@ -35683,10 +35697,10 @@
         <v>201</v>
       </c>
       <c r="Z303" t="s" s="2">
-        <v>956</v>
+        <v>958</v>
       </c>
       <c r="AA303" t="s" s="2">
-        <v>957</v>
+        <v>959</v>
       </c>
       <c r="AB303" t="s" s="2">
         <v>75</v>
@@ -35704,7 +35718,7 @@
         <v>75</v>
       </c>
       <c r="AG303" t="s" s="2">
-        <v>952</v>
+        <v>954</v>
       </c>
       <c r="AH303" t="s" s="2">
         <v>76</v>
@@ -35721,13 +35735,13 @@
     </row>
     <row r="304">
       <c r="A304" t="s" s="2">
-        <v>888</v>
+        <v>890</v>
       </c>
       <c r="B304" t="s" s="2">
-        <v>958</v>
+        <v>960</v>
       </c>
       <c r="C304" t="s" s="2">
-        <v>958</v>
+        <v>960</v>
       </c>
       <c r="D304" s="2"/>
       <c r="E304" t="s" s="2">
@@ -35753,13 +35767,13 @@
         <v>162</v>
       </c>
       <c r="M304" t="s" s="2">
-        <v>959</v>
+        <v>961</v>
       </c>
       <c r="N304" t="s" s="2">
-        <v>960</v>
+        <v>962</v>
       </c>
       <c r="O304" t="s" s="2">
-        <v>961</v>
+        <v>963</v>
       </c>
       <c r="P304" s="2"/>
       <c r="Q304" t="s" s="2">
@@ -35788,10 +35802,10 @@
         <v>173</v>
       </c>
       <c r="Z304" t="s" s="2">
-        <v>962</v>
+        <v>964</v>
       </c>
       <c r="AA304" t="s" s="2">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="AB304" t="s" s="2">
         <v>75</v>
@@ -35809,7 +35823,7 @@
         <v>75</v>
       </c>
       <c r="AG304" t="s" s="2">
-        <v>958</v>
+        <v>960</v>
       </c>
       <c r="AH304" t="s" s="2">
         <v>76</v>
@@ -35826,13 +35840,13 @@
     </row>
     <row r="305">
       <c r="A305" t="s" s="2">
-        <v>888</v>
+        <v>890</v>
       </c>
       <c r="B305" t="s" s="2">
-        <v>963</v>
+        <v>965</v>
       </c>
       <c r="C305" t="s" s="2">
-        <v>963</v>
+        <v>965</v>
       </c>
       <c r="D305" s="2"/>
       <c r="E305" t="s" s="2">
@@ -35855,16 +35869,16 @@
         <v>85</v>
       </c>
       <c r="L305" t="s" s="2">
-        <v>964</v>
+        <v>966</v>
       </c>
       <c r="M305" t="s" s="2">
-        <v>965</v>
+        <v>967</v>
       </c>
       <c r="N305" t="s" s="2">
-        <v>966</v>
+        <v>968</v>
       </c>
       <c r="O305" t="s" s="2">
-        <v>967</v>
+        <v>969</v>
       </c>
       <c r="P305" s="2"/>
       <c r="Q305" t="s" s="2">
@@ -35914,7 +35928,7 @@
         <v>75</v>
       </c>
       <c r="AG305" t="s" s="2">
-        <v>963</v>
+        <v>965</v>
       </c>
       <c r="AH305" t="s" s="2">
         <v>84</v>
@@ -35931,13 +35945,13 @@
     </row>
     <row r="306">
       <c r="A306" t="s" s="2">
-        <v>888</v>
+        <v>890</v>
       </c>
       <c r="B306" t="s" s="2">
-        <v>968</v>
+        <v>970</v>
       </c>
       <c r="C306" t="s" s="2">
-        <v>968</v>
+        <v>970</v>
       </c>
       <c r="D306" s="2"/>
       <c r="E306" t="s" s="2">
@@ -35960,16 +35974,16 @@
         <v>75</v>
       </c>
       <c r="L306" t="s" s="2">
-        <v>964</v>
+        <v>966</v>
       </c>
       <c r="M306" t="s" s="2">
-        <v>969</v>
+        <v>971</v>
       </c>
       <c r="N306" t="s" s="2">
-        <v>970</v>
+        <v>972</v>
       </c>
       <c r="O306" t="s" s="2">
-        <v>971</v>
+        <v>973</v>
       </c>
       <c r="P306" s="2"/>
       <c r="Q306" t="s" s="2">
@@ -36019,7 +36033,7 @@
         <v>75</v>
       </c>
       <c r="AG306" t="s" s="2">
-        <v>968</v>
+        <v>970</v>
       </c>
       <c r="AH306" t="s" s="2">
         <v>76</v>
@@ -36036,13 +36050,13 @@
     </row>
     <row r="307">
       <c r="A307" t="s" s="2">
-        <v>888</v>
+        <v>890</v>
       </c>
       <c r="B307" t="s" s="2">
-        <v>972</v>
+        <v>974</v>
       </c>
       <c r="C307" t="s" s="2">
-        <v>972</v>
+        <v>974</v>
       </c>
       <c r="D307" s="2"/>
       <c r="E307" t="s" s="2">
@@ -36068,10 +36082,10 @@
         <v>237</v>
       </c>
       <c r="M307" t="s" s="2">
-        <v>973</v>
+        <v>975</v>
       </c>
       <c r="N307" t="s" s="2">
-        <v>974</v>
+        <v>976</v>
       </c>
       <c r="O307" s="2"/>
       <c r="P307" s="2"/>
@@ -36122,7 +36136,7 @@
         <v>75</v>
       </c>
       <c r="AG307" t="s" s="2">
-        <v>972</v>
+        <v>974</v>
       </c>
       <c r="AH307" t="s" s="2">
         <v>76</v>
@@ -36139,13 +36153,13 @@
     </row>
     <row r="308">
       <c r="A308" t="s" s="2">
-        <v>888</v>
+        <v>890</v>
       </c>
       <c r="B308" t="s" s="2">
-        <v>975</v>
+        <v>977</v>
       </c>
       <c r="C308" t="s" s="2">
-        <v>975</v>
+        <v>977</v>
       </c>
       <c r="D308" s="2"/>
       <c r="E308" t="s" s="2">
@@ -36242,13 +36256,13 @@
     </row>
     <row r="309">
       <c r="A309" t="s" s="2">
-        <v>888</v>
+        <v>890</v>
       </c>
       <c r="B309" t="s" s="2">
-        <v>976</v>
+        <v>978</v>
       </c>
       <c r="C309" t="s" s="2">
-        <v>976</v>
+        <v>978</v>
       </c>
       <c r="D309" s="2"/>
       <c r="E309" t="s" s="2">
@@ -36347,13 +36361,13 @@
     </row>
     <row r="310">
       <c r="A310" t="s" s="2">
-        <v>888</v>
+        <v>890</v>
       </c>
       <c r="B310" t="s" s="2">
-        <v>977</v>
+        <v>979</v>
       </c>
       <c r="C310" t="s" s="2">
-        <v>977</v>
+        <v>979</v>
       </c>
       <c r="D310" s="2"/>
       <c r="E310" t="s" s="2">
@@ -36454,13 +36468,13 @@
     </row>
     <row r="311">
       <c r="A311" t="s" s="2">
-        <v>888</v>
+        <v>890</v>
       </c>
       <c r="B311" t="s" s="2">
-        <v>978</v>
+        <v>980</v>
       </c>
       <c r="C311" t="s" s="2">
-        <v>978</v>
+        <v>980</v>
       </c>
       <c r="D311" s="2"/>
       <c r="E311" t="s" s="2">
@@ -36486,10 +36500,10 @@
         <v>104</v>
       </c>
       <c r="M311" t="s" s="2">
-        <v>979</v>
+        <v>981</v>
       </c>
       <c r="N311" t="s" s="2">
-        <v>980</v>
+        <v>982</v>
       </c>
       <c r="O311" s="2"/>
       <c r="P311" s="2"/>
@@ -36498,7 +36512,7 @@
       </c>
       <c r="R311" s="2"/>
       <c r="S311" t="s" s="2">
-        <v>981</v>
+        <v>983</v>
       </c>
       <c r="T311" t="s" s="2">
         <v>75</v>
@@ -36519,10 +36533,10 @@
         <v>152</v>
       </c>
       <c r="Z311" t="s" s="2">
-        <v>982</v>
+        <v>984</v>
       </c>
       <c r="AA311" t="s" s="2">
-        <v>983</v>
+        <v>985</v>
       </c>
       <c r="AB311" t="s" s="2">
         <v>75</v>
@@ -36540,7 +36554,7 @@
         <v>75</v>
       </c>
       <c r="AG311" t="s" s="2">
-        <v>978</v>
+        <v>980</v>
       </c>
       <c r="AH311" t="s" s="2">
         <v>84</v>
@@ -36557,13 +36571,13 @@
     </row>
     <row r="312">
       <c r="A312" t="s" s="2">
-        <v>888</v>
+        <v>890</v>
       </c>
       <c r="B312" t="s" s="2">
-        <v>984</v>
+        <v>986</v>
       </c>
       <c r="C312" t="s" s="2">
-        <v>984</v>
+        <v>986</v>
       </c>
       <c r="D312" s="2"/>
       <c r="E312" t="s" s="2">
@@ -36586,16 +36600,16 @@
         <v>85</v>
       </c>
       <c r="L312" t="s" s="2">
-        <v>985</v>
+        <v>987</v>
       </c>
       <c r="M312" t="s" s="2">
-        <v>986</v>
+        <v>988</v>
       </c>
       <c r="N312" t="s" s="2">
-        <v>987</v>
+        <v>989</v>
       </c>
       <c r="O312" t="s" s="2">
-        <v>988</v>
+        <v>990</v>
       </c>
       <c r="P312" s="2"/>
       <c r="Q312" t="s" s="2">
@@ -36645,7 +36659,7 @@
         <v>75</v>
       </c>
       <c r="AG312" t="s" s="2">
-        <v>984</v>
+        <v>986</v>
       </c>
       <c r="AH312" t="s" s="2">
         <v>84</v>
@@ -36662,13 +36676,13 @@
     </row>
     <row r="313">
       <c r="A313" t="s" s="2">
-        <v>888</v>
+        <v>890</v>
       </c>
       <c r="B313" t="s" s="2">
-        <v>989</v>
+        <v>991</v>
       </c>
       <c r="C313" t="s" s="2">
-        <v>989</v>
+        <v>991</v>
       </c>
       <c r="D313" s="2"/>
       <c r="E313" t="s" s="2">
@@ -36765,13 +36779,13 @@
     </row>
     <row r="314">
       <c r="A314" t="s" s="2">
-        <v>888</v>
+        <v>890</v>
       </c>
       <c r="B314" t="s" s="2">
-        <v>990</v>
+        <v>992</v>
       </c>
       <c r="C314" t="s" s="2">
-        <v>990</v>
+        <v>992</v>
       </c>
       <c r="D314" s="2"/>
       <c r="E314" t="s" s="2">
@@ -36870,13 +36884,13 @@
     </row>
     <row r="315">
       <c r="A315" t="s" s="2">
-        <v>888</v>
+        <v>890</v>
       </c>
       <c r="B315" t="s" s="2">
-        <v>991</v>
+        <v>993</v>
       </c>
       <c r="C315" t="s" s="2">
-        <v>991</v>
+        <v>993</v>
       </c>
       <c r="D315" s="2"/>
       <c r="E315" t="s" s="2">
@@ -36975,13 +36989,13 @@
     </row>
     <row r="316">
       <c r="A316" t="s" s="2">
-        <v>888</v>
+        <v>890</v>
       </c>
       <c r="B316" t="s" s="2">
-        <v>992</v>
+        <v>994</v>
       </c>
       <c r="C316" t="s" s="2">
-        <v>992</v>
+        <v>994</v>
       </c>
       <c r="D316" s="2"/>
       <c r="E316" t="s" s="2">
@@ -37080,13 +37094,13 @@
     </row>
     <row r="317">
       <c r="A317" t="s" s="2">
-        <v>888</v>
+        <v>890</v>
       </c>
       <c r="B317" t="s" s="2">
-        <v>993</v>
+        <v>995</v>
       </c>
       <c r="C317" t="s" s="2">
-        <v>993</v>
+        <v>995</v>
       </c>
       <c r="D317" s="2"/>
       <c r="E317" t="s" s="2">
@@ -37185,13 +37199,13 @@
     </row>
     <row r="318">
       <c r="A318" t="s" s="2">
-        <v>888</v>
+        <v>890</v>
       </c>
       <c r="B318" t="s" s="2">
-        <v>994</v>
+        <v>996</v>
       </c>
       <c r="C318" t="s" s="2">
-        <v>994</v>
+        <v>996</v>
       </c>
       <c r="D318" s="2"/>
       <c r="E318" t="s" s="2">
@@ -37290,13 +37304,13 @@
     </row>
     <row r="319">
       <c r="A319" t="s" s="2">
-        <v>888</v>
+        <v>890</v>
       </c>
       <c r="B319" t="s" s="2">
-        <v>995</v>
+        <v>997</v>
       </c>
       <c r="C319" t="s" s="2">
-        <v>995</v>
+        <v>997</v>
       </c>
       <c r="D319" s="2"/>
       <c r="E319" t="s" s="2">
@@ -37322,13 +37336,13 @@
         <v>78</v>
       </c>
       <c r="M319" t="s" s="2">
-        <v>996</v>
+        <v>998</v>
       </c>
       <c r="N319" t="s" s="2">
-        <v>997</v>
+        <v>999</v>
       </c>
       <c r="O319" t="s" s="2">
-        <v>998</v>
+        <v>1000</v>
       </c>
       <c r="P319" s="2"/>
       <c r="Q319" t="s" s="2">
@@ -37378,7 +37392,7 @@
         <v>75</v>
       </c>
       <c r="AG319" t="s" s="2">
-        <v>995</v>
+        <v>997</v>
       </c>
       <c r="AH319" t="s" s="2">
         <v>76</v>
@@ -37395,13 +37409,13 @@
     </row>
     <row r="320">
       <c r="A320" t="s" s="2">
-        <v>888</v>
+        <v>890</v>
       </c>
       <c r="B320" t="s" s="2">
-        <v>999</v>
+        <v>1001</v>
       </c>
       <c r="C320" t="s" s="2">
-        <v>999</v>
+        <v>1001</v>
       </c>
       <c r="D320" s="2"/>
       <c r="E320" t="s" s="2">
@@ -37424,13 +37438,13 @@
         <v>75</v>
       </c>
       <c r="L320" t="s" s="2">
-        <v>1000</v>
+        <v>1002</v>
       </c>
       <c r="M320" t="s" s="2">
-        <v>1001</v>
+        <v>1003</v>
       </c>
       <c r="N320" t="s" s="2">
-        <v>1002</v>
+        <v>1004</v>
       </c>
       <c r="O320" s="2"/>
       <c r="P320" s="2"/>
@@ -37481,7 +37495,7 @@
         <v>75</v>
       </c>
       <c r="AG320" t="s" s="2">
-        <v>999</v>
+        <v>1001</v>
       </c>
       <c r="AH320" t="s" s="2">
         <v>76</v>
@@ -37498,13 +37512,13 @@
     </row>
     <row r="321">
       <c r="A321" t="s" s="2">
-        <v>888</v>
+        <v>890</v>
       </c>
       <c r="B321" t="s" s="2">
-        <v>1003</v>
+        <v>1005</v>
       </c>
       <c r="C321" t="s" s="2">
-        <v>1003</v>
+        <v>1005</v>
       </c>
       <c r="D321" s="2"/>
       <c r="E321" t="s" s="2">
@@ -37601,13 +37615,13 @@
     </row>
     <row r="322">
       <c r="A322" t="s" s="2">
-        <v>888</v>
+        <v>890</v>
       </c>
       <c r="B322" t="s" s="2">
-        <v>1004</v>
+        <v>1006</v>
       </c>
       <c r="C322" t="s" s="2">
-        <v>1004</v>
+        <v>1006</v>
       </c>
       <c r="D322" s="2"/>
       <c r="E322" t="s" s="2">
@@ -37704,16 +37718,16 @@
     </row>
     <row r="323">
       <c r="A323" t="s" s="2">
-        <v>888</v>
+        <v>890</v>
       </c>
       <c r="B323" t="s" s="2">
-        <v>1005</v>
+        <v>1007</v>
       </c>
       <c r="C323" t="s" s="2">
-        <v>1004</v>
+        <v>1006</v>
       </c>
       <c r="D323" t="s" s="2">
-        <v>1006</v>
+        <v>1008</v>
       </c>
       <c r="E323" t="s" s="2">
         <v>75</v>
@@ -37735,7 +37749,7 @@
         <v>75</v>
       </c>
       <c r="L323" t="s" s="2">
-        <v>1007</v>
+        <v>1009</v>
       </c>
       <c r="M323" t="s" s="2">
         <v>445</v>
@@ -37809,13 +37823,13 @@
     </row>
     <row r="324">
       <c r="A324" t="s" s="2">
-        <v>888</v>
+        <v>890</v>
       </c>
       <c r="B324" t="s" s="2">
-        <v>1008</v>
+        <v>1010</v>
       </c>
       <c r="C324" t="s" s="2">
-        <v>1009</v>
+        <v>1011</v>
       </c>
       <c r="D324" s="2"/>
       <c r="E324" t="s" s="2">
@@ -37912,13 +37926,13 @@
     </row>
     <row r="325">
       <c r="A325" t="s" s="2">
-        <v>888</v>
+        <v>890</v>
       </c>
       <c r="B325" t="s" s="2">
-        <v>1010</v>
+        <v>1012</v>
       </c>
       <c r="C325" t="s" s="2">
-        <v>1011</v>
+        <v>1013</v>
       </c>
       <c r="D325" s="2"/>
       <c r="E325" t="s" s="2">
@@ -38017,13 +38031,13 @@
     </row>
     <row r="326">
       <c r="A326" t="s" s="2">
-        <v>888</v>
+        <v>890</v>
       </c>
       <c r="B326" t="s" s="2">
-        <v>1012</v>
+        <v>1014</v>
       </c>
       <c r="C326" t="s" s="2">
-        <v>1013</v>
+        <v>1015</v>
       </c>
       <c r="D326" s="2"/>
       <c r="E326" t="s" s="2">
@@ -38063,7 +38077,7 @@
       </c>
       <c r="R326" s="2"/>
       <c r="S326" t="s" s="2">
-        <v>1014</v>
+        <v>1016</v>
       </c>
       <c r="T326" t="s" s="2">
         <v>75</v>
@@ -38122,13 +38136,13 @@
     </row>
     <row r="327">
       <c r="A327" t="s" s="2">
-        <v>888</v>
+        <v>890</v>
       </c>
       <c r="B327" t="s" s="2">
-        <v>1015</v>
+        <v>1017</v>
       </c>
       <c r="C327" t="s" s="2">
-        <v>1016</v>
+        <v>1018</v>
       </c>
       <c r="D327" s="2"/>
       <c r="E327" t="s" s="2">
@@ -38225,13 +38239,13 @@
     </row>
     <row r="328">
       <c r="A328" t="s" s="2">
-        <v>888</v>
+        <v>890</v>
       </c>
       <c r="B328" t="s" s="2">
-        <v>1017</v>
+        <v>1019</v>
       </c>
       <c r="C328" t="s" s="2">
-        <v>1017</v>
+        <v>1019</v>
       </c>
       <c r="D328" s="2"/>
       <c r="E328" t="s" s="2">
@@ -38257,13 +38271,13 @@
         <v>338</v>
       </c>
       <c r="M328" t="s" s="2">
-        <v>1018</v>
+        <v>1020</v>
       </c>
       <c r="N328" t="s" s="2">
-        <v>1019</v>
+        <v>1021</v>
       </c>
       <c r="O328" t="s" s="2">
-        <v>1020</v>
+        <v>1022</v>
       </c>
       <c r="P328" s="2"/>
       <c r="Q328" t="s" s="2">
@@ -38293,7 +38307,7 @@
       </c>
       <c r="Z328" s="2"/>
       <c r="AA328" t="s" s="2">
-        <v>1021</v>
+        <v>1023</v>
       </c>
       <c r="AB328" t="s" s="2">
         <v>75</v>
@@ -38311,7 +38325,7 @@
         <v>75</v>
       </c>
       <c r="AG328" t="s" s="2">
-        <v>1022</v>
+        <v>1024</v>
       </c>
       <c r="AH328" t="s" s="2">
         <v>84</v>
@@ -38328,13 +38342,13 @@
     </row>
     <row r="329">
       <c r="A329" t="s" s="2">
-        <v>888</v>
+        <v>890</v>
       </c>
       <c r="B329" t="s" s="2">
-        <v>1023</v>
+        <v>1025</v>
       </c>
       <c r="C329" t="s" s="2">
-        <v>1023</v>
+        <v>1025</v>
       </c>
       <c r="D329" s="2"/>
       <c r="E329" t="s" s="2">
@@ -38431,13 +38445,13 @@
     </row>
     <row r="330">
       <c r="A330" t="s" s="2">
-        <v>888</v>
+        <v>890</v>
       </c>
       <c r="B330" t="s" s="2">
-        <v>1024</v>
+        <v>1026</v>
       </c>
       <c r="C330" t="s" s="2">
-        <v>1024</v>
+        <v>1026</v>
       </c>
       <c r="D330" s="2"/>
       <c r="E330" t="s" s="2">
@@ -38536,13 +38550,13 @@
     </row>
     <row r="331">
       <c r="A331" t="s" s="2">
-        <v>888</v>
+        <v>890</v>
       </c>
       <c r="B331" t="s" s="2">
-        <v>1025</v>
+        <v>1027</v>
       </c>
       <c r="C331" t="s" s="2">
-        <v>1025</v>
+        <v>1027</v>
       </c>
       <c r="D331" s="2"/>
       <c r="E331" t="s" s="2">
@@ -38643,13 +38657,13 @@
     </row>
     <row r="332">
       <c r="A332" t="s" s="2">
-        <v>888</v>
+        <v>890</v>
       </c>
       <c r="B332" t="s" s="2">
-        <v>1026</v>
+        <v>1028</v>
       </c>
       <c r="C332" t="s" s="2">
-        <v>1026</v>
+        <v>1028</v>
       </c>
       <c r="D332" s="2"/>
       <c r="E332" t="s" s="2">
@@ -38748,13 +38762,13 @@
     </row>
     <row r="333">
       <c r="A333" t="s" s="2">
-        <v>888</v>
+        <v>890</v>
       </c>
       <c r="B333" t="s" s="2">
-        <v>1027</v>
+        <v>1029</v>
       </c>
       <c r="C333" t="s" s="2">
-        <v>1027</v>
+        <v>1029</v>
       </c>
       <c r="D333" s="2"/>
       <c r="E333" t="s" s="2">
@@ -38853,13 +38867,13 @@
     </row>
     <row r="334">
       <c r="A334" t="s" s="2">
-        <v>888</v>
+        <v>890</v>
       </c>
       <c r="B334" t="s" s="2">
-        <v>1028</v>
+        <v>1030</v>
       </c>
       <c r="C334" t="s" s="2">
-        <v>1028</v>
+        <v>1030</v>
       </c>
       <c r="D334" s="2"/>
       <c r="E334" t="s" s="2">
@@ -38958,13 +38972,13 @@
     </row>
     <row r="335">
       <c r="A335" t="s" s="2">
-        <v>888</v>
+        <v>890</v>
       </c>
       <c r="B335" t="s" s="2">
-        <v>1029</v>
+        <v>1031</v>
       </c>
       <c r="C335" t="s" s="2">
-        <v>1029</v>
+        <v>1031</v>
       </c>
       <c r="D335" s="2"/>
       <c r="E335" t="s" s="2">
@@ -39065,13 +39079,13 @@
     </row>
     <row r="336">
       <c r="A336" t="s" s="2">
-        <v>888</v>
+        <v>890</v>
       </c>
       <c r="B336" t="s" s="2">
-        <v>1030</v>
+        <v>1032</v>
       </c>
       <c r="C336" t="s" s="2">
-        <v>1030</v>
+        <v>1032</v>
       </c>
       <c r="D336" s="2"/>
       <c r="E336" t="s" s="2">
@@ -39097,13 +39111,13 @@
         <v>217</v>
       </c>
       <c r="M336" t="s" s="2">
-        <v>1031</v>
+        <v>1033</v>
       </c>
       <c r="N336" t="s" s="2">
-        <v>1032</v>
+        <v>1034</v>
       </c>
       <c r="O336" t="s" s="2">
-        <v>1033</v>
+        <v>1035</v>
       </c>
       <c r="P336" s="2"/>
       <c r="Q336" t="s" s="2">
@@ -39153,7 +39167,7 @@
         <v>75</v>
       </c>
       <c r="AG336" t="s" s="2">
-        <v>1034</v>
+        <v>1036</v>
       </c>
       <c r="AH336" t="s" s="2">
         <v>84</v>
@@ -39170,13 +39184,13 @@
     </row>
     <row r="337">
       <c r="A337" t="s" s="2">
-        <v>888</v>
+        <v>890</v>
       </c>
       <c r="B337" t="s" s="2">
-        <v>1035</v>
+        <v>1037</v>
       </c>
       <c r="C337" t="s" s="2">
-        <v>1035</v>
+        <v>1037</v>
       </c>
       <c r="D337" s="2"/>
       <c r="E337" t="s" s="2">
@@ -39199,16 +39213,16 @@
         <v>85</v>
       </c>
       <c r="L337" t="s" s="2">
-        <v>964</v>
+        <v>966</v>
       </c>
       <c r="M337" t="s" s="2">
-        <v>1036</v>
+        <v>1038</v>
       </c>
       <c r="N337" t="s" s="2">
-        <v>1037</v>
+        <v>1039</v>
       </c>
       <c r="O337" t="s" s="2">
-        <v>1033</v>
+        <v>1035</v>
       </c>
       <c r="P337" s="2"/>
       <c r="Q337" t="s" s="2">
@@ -39258,7 +39272,7 @@
         <v>75</v>
       </c>
       <c r="AG337" t="s" s="2">
-        <v>1038</v>
+        <v>1040</v>
       </c>
       <c r="AH337" t="s" s="2">
         <v>84</v>
@@ -39275,13 +39289,13 @@
     </row>
     <row r="338">
       <c r="A338" t="s" s="2">
-        <v>888</v>
+        <v>890</v>
       </c>
       <c r="B338" t="s" s="2">
-        <v>1039</v>
+        <v>1041</v>
       </c>
       <c r="C338" t="s" s="2">
-        <v>1039</v>
+        <v>1041</v>
       </c>
       <c r="D338" s="2"/>
       <c r="E338" t="s" s="2">
@@ -39304,19 +39318,19 @@
         <v>85</v>
       </c>
       <c r="L338" t="s" s="2">
-        <v>964</v>
+        <v>966</v>
       </c>
       <c r="M338" t="s" s="2">
-        <v>1040</v>
+        <v>1042</v>
       </c>
       <c r="N338" t="s" s="2">
-        <v>1041</v>
+        <v>1043</v>
       </c>
       <c r="O338" t="s" s="2">
-        <v>1042</v>
+        <v>1044</v>
       </c>
       <c r="P338" t="s" s="2">
-        <v>1043</v>
+        <v>1045</v>
       </c>
       <c r="Q338" t="s" s="2">
         <v>75</v>
@@ -39365,7 +39379,7 @@
         <v>75</v>
       </c>
       <c r="AG338" t="s" s="2">
-        <v>1044</v>
+        <v>1046</v>
       </c>
       <c r="AH338" t="s" s="2">
         <v>76</v>
@@ -39382,13 +39396,13 @@
     </row>
     <row r="339">
       <c r="A339" t="s" s="2">
-        <v>888</v>
+        <v>890</v>
       </c>
       <c r="B339" t="s" s="2">
-        <v>1045</v>
+        <v>1047</v>
       </c>
       <c r="C339" t="s" s="2">
-        <v>1045</v>
+        <v>1047</v>
       </c>
       <c r="D339" s="2"/>
       <c r="E339" t="s" s="2">
@@ -39414,13 +39428,13 @@
         <v>104</v>
       </c>
       <c r="M339" t="s" s="2">
-        <v>1046</v>
+        <v>1048</v>
       </c>
       <c r="N339" t="s" s="2">
-        <v>1047</v>
+        <v>1049</v>
       </c>
       <c r="O339" t="s" s="2">
-        <v>1048</v>
+        <v>1050</v>
       </c>
       <c r="P339" s="2"/>
       <c r="Q339" t="s" s="2">
@@ -39470,7 +39484,7 @@
         <v>75</v>
       </c>
       <c r="AG339" t="s" s="2">
-        <v>1049</v>
+        <v>1051</v>
       </c>
       <c r="AH339" t="s" s="2">
         <v>76</v>
@@ -39487,13 +39501,13 @@
     </row>
     <row r="340">
       <c r="A340" t="s" s="2">
-        <v>888</v>
+        <v>890</v>
       </c>
       <c r="B340" t="s" s="2">
-        <v>1050</v>
+        <v>1052</v>
       </c>
       <c r="C340" t="s" s="2">
-        <v>1050</v>
+        <v>1052</v>
       </c>
       <c r="D340" s="2"/>
       <c r="E340" t="s" s="2">
@@ -39519,10 +39533,10 @@
         <v>104</v>
       </c>
       <c r="M340" t="s" s="2">
-        <v>1051</v>
+        <v>1053</v>
       </c>
       <c r="N340" t="s" s="2">
-        <v>1052</v>
+        <v>1054</v>
       </c>
       <c r="O340" s="2"/>
       <c r="P340" s="2"/>
@@ -39573,7 +39587,7 @@
         <v>75</v>
       </c>
       <c r="AG340" t="s" s="2">
-        <v>1053</v>
+        <v>1055</v>
       </c>
       <c r="AH340" t="s" s="2">
         <v>76</v>
@@ -39590,13 +39604,13 @@
     </row>
     <row r="341">
       <c r="A341" t="s" s="2">
-        <v>888</v>
+        <v>890</v>
       </c>
       <c r="B341" t="s" s="2">
-        <v>1054</v>
+        <v>1056</v>
       </c>
       <c r="C341" t="s" s="2">
-        <v>1054</v>
+        <v>1056</v>
       </c>
       <c r="D341" s="2"/>
       <c r="E341" t="s" s="2">
@@ -39622,13 +39636,13 @@
         <v>298</v>
       </c>
       <c r="M341" t="s" s="2">
-        <v>1055</v>
+        <v>1057</v>
       </c>
       <c r="N341" t="s" s="2">
-        <v>1056</v>
+        <v>1058</v>
       </c>
       <c r="O341" t="s" s="2">
-        <v>1057</v>
+        <v>1059</v>
       </c>
       <c r="P341" s="2"/>
       <c r="Q341" t="s" s="2">
@@ -39678,7 +39692,7 @@
         <v>75</v>
       </c>
       <c r="AG341" t="s" s="2">
-        <v>1058</v>
+        <v>1060</v>
       </c>
       <c r="AH341" t="s" s="2">
         <v>76</v>

--- a/branches/migration/2027.0.0-ballot.rc1-template-v0.13.2/all-profiles.xlsx
+++ b/branches/migration/2027.0.0-ballot.rc1-template-v0.13.2/all-profiles.xlsx
@@ -24,7 +24,7 @@
     <t>ID</t>
   </si>
   <si>
-    <t>56375452-bfa1-4111-af7c-5b5ba9a1857c</t>
+    <t>mii-pr-consent-documentreference</t>
   </si>
   <si>
     <t>URL</t>
@@ -1221,7 +1221,7 @@
     <t>May be identifiers or resources that caused the DocumentReference or referenced Document to be created.</t>
   </si>
   <si>
-    <t>e0e166b4-0f77-478d-9062-de0034d98ce0</t>
+    <t>mii-pr-consent-einwilligung</t>
   </si>
   <si>
     <t>https://www.medizininformatik-initiative.de/fhir/modul-consent/StructureDefinition/mii-pr-consent-einwilligung</t>
@@ -2773,7 +2773,7 @@
     <t>Consent.provision.provision.provision</t>
   </si>
   <si>
-    <t>f675b1e8-9f3f-44e8-bb59-9681f78eb464</t>
+    <t>mii-pr-consent-provenance</t>
   </si>
   <si>
     <t>https://www.medizininformatik-initiative.de/fhir/modul-consent/StructureDefinition/mii-pr-consent-provenance</t>
@@ -3929,7 +3929,7 @@
   <dimension ref="A1:AK341"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="34.44140625" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="28.37109375" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="61.21484375" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="43.578125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="14.80078125" customWidth="true" bestFit="true" hidden="true"/>
